--- a/outputs/reports/comparison/feature_importance_top10_all.xlsx
+++ b/outputs/reports/comparison/feature_importance_top10_all.xlsx
@@ -474,19 +474,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07476412271520354</v>
+        <v>0.06671461789117154</v>
       </c>
       <c r="F2" t="n">
-        <v>7.476412271520343</v>
+        <v>6.671461789117155</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -495,7 +495,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06525520175242064</v>
+        <v>0.06495441989195058</v>
       </c>
       <c r="F3" t="n">
-        <v>6.525520175242055</v>
+        <v>6.495441989195059</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.53%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -546,19 +546,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.06142095487706396</v>
+        <v>0.05547755973096497</v>
       </c>
       <c r="F4" t="n">
-        <v>6.142095487706388</v>
+        <v>5.547755973096498</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.14%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.55%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -582,19 +582,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.04453851651510576</v>
+        <v>0.05417814811546744</v>
       </c>
       <c r="F5" t="n">
-        <v>4.453851651510569</v>
+        <v>5.417814811546745</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.45%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -618,19 +618,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04184806361799587</v>
+        <v>0.05058522443296955</v>
       </c>
       <c r="F6" t="n">
-        <v>4.184806361799581</v>
+        <v>5.058522443296956</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.18%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -654,19 +654,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.03966638691246891</v>
+        <v>0.04458071949171321</v>
       </c>
       <c r="F7" t="n">
-        <v>3.966638691246886</v>
+        <v>4.458071949171321</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=3.97%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.46%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -690,19 +690,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.03890392119087331</v>
+        <v>0.04060187085898578</v>
       </c>
       <c r="F8" t="n">
-        <v>3.890392119087326</v>
+        <v>4.060187085898579</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.89%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -726,19 +726,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03803318886386643</v>
+        <v>0.03611816776722611</v>
       </c>
       <c r="F9" t="n">
-        <v>3.803318886386638</v>
+        <v>3.611816776722611</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.80%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -762,19 +762,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대표자불일치여부</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03769171190310019</v>
+        <v>0.03477271178468273</v>
       </c>
       <c r="F10" t="n">
-        <v>3.769171190310014</v>
+        <v>3.477271178468274</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=3.77%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -798,19 +798,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03669786363562316</v>
+        <v>0.0344039068366</v>
       </c>
       <c r="F11" t="n">
-        <v>3.669786363562311</v>
+        <v>3.44039068366</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.44%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -834,19 +834,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.1703765778033789</v>
+        <v>0.1027335695024538</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01773032250328394</v>
+        <v>0.006969778495202472</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=17.04%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=10.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -870,19 +870,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.1219556905672209</v>
+        <v>0.09652091154231966</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01269137901902762</v>
+        <v>0.006548291633037551</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=12.20%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=9.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -906,19 +906,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.08969255748179694</v>
+        <v>0.07809443240098939</v>
       </c>
       <c r="F14" t="n">
-        <v>0.009333900180409971</v>
+        <v>0.005298179535467795</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=8.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -942,19 +942,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.07269679987429753</v>
+        <v>0.06968751652302239</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00756522829220968</v>
+        <v>0.00472782710070857</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=7.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -978,19 +978,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>지자체수행보조사업수</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.05321321950452901</v>
+        <v>0.05950933220535835</v>
       </c>
       <c r="F16" t="n">
-        <v>0.005537659902654923</v>
+        <v>0.004037306071204505</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=5.32%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1014,19 +1014,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.05130152411878593</v>
+        <v>0.05448633215248471</v>
       </c>
       <c r="F17" t="n">
-        <v>0.005338718380561547</v>
+        <v>0.003696529459241427</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.13%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1050,19 +1050,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LBST_EXE_SUM_AMT</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>인건비집행합계금액</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.04928507830094729</v>
+        <v>0.04909321630624239</v>
       </c>
       <c r="F18" t="n">
-        <v>0.005128875953147982</v>
+        <v>0.003330642991660082</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비집행합계금액(LBST_EXE_SUM_AMT). 기여도(정규화 비중)=4.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1086,19 +1086,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.04705913161891651</v>
+        <v>0.04446676888912223</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00489723171509393</v>
+        <v>0.003016769796430951</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=4.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1122,19 +1122,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.04588068925784221</v>
+        <v>0.03666790038597665</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00477459653024187</v>
+        <v>0.002487669267330406</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=4.59%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1158,19 +1158,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>보조금전용신용카드집행건수</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.04224061174252269</v>
+        <v>0.0365357161740591</v>
       </c>
       <c r="F21" t="n">
-        <v>0.004395790070365391</v>
+        <v>0.002478701461752442</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.22%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=3.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1194,19 +1194,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.2354919926285472</v>
+        <v>0.2770684556012389</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06181358361811956</v>
+        <v>0.0551125459600037</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=27.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1230,19 +1230,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.1389882420120957</v>
+        <v>0.1703274904421835</v>
       </c>
       <c r="F23" t="n">
-        <v>0.03648260488033528</v>
+        <v>0.03388036947358997</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=13.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=17.03%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1266,19 +1266,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.1307135255794641</v>
+        <v>0.1166684700281321</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03431059949528809</v>
+        <v>0.02320688727468401</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=13.07%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=11.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1302,19 +1302,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.09743296908661454</v>
+        <v>0.1080844694510566</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02557488649432327</v>
+        <v>0.02149941709263758</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=9.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=10.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1338,19 +1338,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.09413657954162016</v>
+        <v>0.09138534227800571</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02470962713453345</v>
+        <v>0.01817774190655552</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=9.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.14%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1374,19 +1374,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.09272458276014207</v>
+        <v>0.06511938252903433</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02433899635364706</v>
+        <v>0.01295309837682734</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=9.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1410,19 +1410,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.07495003504036123</v>
+        <v>0.06332503787059059</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01967340887660712</v>
+        <v>0.01259617971482385</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=7.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=6.33%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.05975030498092234</v>
+        <v>0.040269061530693</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01568367752941874</v>
+        <v>0.008010043942247358</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.98%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.03%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1482,19 +1482,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.02560282399356293</v>
+        <v>0.02744716150905338</v>
       </c>
       <c r="F30" t="n">
-        <v>0.006720408129895161</v>
+        <v>0.00545960003587137</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=2.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=2.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1518,19 +1518,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_CLT_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>당월개인사업자거래처수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.009094920445401911</v>
+        <v>0.01709586669552097</v>
       </c>
       <c r="F31" t="n">
-        <v>0.002387298265120907</v>
+        <v>0.00340059187516828</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>변수 의미: 당월개인사업자거래처수(TMNT_INDV_BZR_CLT_NUM). 기여도(정규화 비중)=0.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=1.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.3551872132603224</v>
+        <v>0.2989836767503042</v>
       </c>
       <c r="F32" t="n">
-        <v>0.09156760468956948</v>
+        <v>0.06737871042955795</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=35.52%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=29.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.1210067866128246</v>
+        <v>0.1900691609165165</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03119566580004468</v>
+        <v>0.04283382656264023</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=12.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=19.01%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1626,19 +1626,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.09550941880378003</v>
+        <v>0.1094318299389545</v>
       </c>
       <c r="F34" t="n">
-        <v>0.024622419891972</v>
+        <v>0.02466146533943159</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=9.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=10.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1662,19 +1662,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.08317300577179218</v>
+        <v>0.09961877929788324</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02144208076480753</v>
+        <v>0.02245000448390294</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=8.32%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=9.96%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1698,19 +1698,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0470834478530202</v>
+        <v>0.0671473708505427</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01213815807402807</v>
+        <v>0.01513227513227527</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1734,19 +1734,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.04409184126514275</v>
+        <v>0.04746555881861263</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01136691902262477</v>
+        <v>0.01069679849340871</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1770,19 +1770,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.04333072580815647</v>
+        <v>0.03771617760586961</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01117070272686144</v>
+        <v>0.008499686126804851</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.33%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.77%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1806,19 +1806,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.03891202773842957</v>
+        <v>0.03252711919712811</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01003155812090184</v>
+        <v>0.007330284279436938</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.89%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=3.25%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1842,19 +1842,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.03607898687075828</v>
+        <v>0.01931571281904346</v>
       </c>
       <c r="F40" t="n">
-        <v>0.009301197464449407</v>
+        <v>0.004352972827549206</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=3.61%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=1.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1878,19 +1878,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.01897503118459181</v>
+        <v>0.01564676201163554</v>
       </c>
       <c r="F41" t="n">
-        <v>0.004891781262433892</v>
+        <v>0.003526141153259887</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=1.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=1.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.0700729582360157</v>
+        <v>0.07123498568589968</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0700729582360157</v>
+        <v>0.07123498568589968</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.01%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.06148273354766497</v>
+        <v>0.06438996081869364</v>
       </c>
       <c r="F43" t="n">
-        <v>0.06148273354766497</v>
+        <v>0.06438996081869364</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.15%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.44%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.05878294907501541</v>
+        <v>0.05839048873031386</v>
       </c>
       <c r="F44" t="n">
-        <v>0.05878294907501541</v>
+        <v>0.05839048873031386</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.88%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2022,19 +2022,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.05384256859475585</v>
+        <v>0.05427018714487944</v>
       </c>
       <c r="F45" t="n">
-        <v>0.05384256859475585</v>
+        <v>0.05427018714487944</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.38%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.43%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.0527039178199459</v>
+        <v>0.05358114621860463</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0527039178199459</v>
+        <v>0.05358114621860463</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.27%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2094,19 +2094,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.04792607095040281</v>
+        <v>0.05098330684009479</v>
       </c>
       <c r="F47" t="n">
-        <v>0.04792607095040281</v>
+        <v>0.05098330684009479</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.79%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.10%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2130,19 +2130,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.04662512948148972</v>
+        <v>0.04893369782155989</v>
       </c>
       <c r="F48" t="n">
-        <v>0.04662512948148972</v>
+        <v>0.04893369782155989</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.66%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.04540918801236458</v>
+        <v>0.04303240847945023</v>
       </c>
       <c r="F49" t="n">
-        <v>0.04540918801236458</v>
+        <v>0.04303240847945023</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.54%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.03300190271002322</v>
+        <v>0.03644836213775499</v>
       </c>
       <c r="F50" t="n">
-        <v>0.03300190271002322</v>
+        <v>0.03644836213775499</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.64%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2238,19 +2238,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.03110928199837388</v>
+        <v>0.02993899235451626</v>
       </c>
       <c r="F51" t="n">
-        <v>0.03110928199837388</v>
+        <v>0.02993899235451626</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.11%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2330,19 +2330,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07476412271520354</v>
+        <v>0.06671461789117154</v>
       </c>
       <c r="F2" t="n">
-        <v>7.476412271520343</v>
+        <v>6.671461789117155</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06525520175242064</v>
+        <v>0.06495441989195058</v>
       </c>
       <c r="F3" t="n">
-        <v>6.525520175242055</v>
+        <v>6.495441989195059</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.53%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2402,19 +2402,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.06142095487706396</v>
+        <v>0.05547755973096497</v>
       </c>
       <c r="F4" t="n">
-        <v>6.142095487706388</v>
+        <v>5.547755973096498</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.14%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.55%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2438,19 +2438,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.04453851651510576</v>
+        <v>0.05417814811546744</v>
       </c>
       <c r="F5" t="n">
-        <v>4.453851651510569</v>
+        <v>5.417814811546745</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.45%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2474,19 +2474,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04184806361799587</v>
+        <v>0.05058522443296955</v>
       </c>
       <c r="F6" t="n">
-        <v>4.184806361799581</v>
+        <v>5.058522443296956</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.18%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2510,19 +2510,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.03966638691246891</v>
+        <v>0.04458071949171321</v>
       </c>
       <c r="F7" t="n">
-        <v>3.966638691246886</v>
+        <v>4.458071949171321</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=3.97%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.46%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2546,19 +2546,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.03890392119087331</v>
+        <v>0.04060187085898578</v>
       </c>
       <c r="F8" t="n">
-        <v>3.890392119087326</v>
+        <v>4.060187085898579</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.89%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2582,19 +2582,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03803318886386643</v>
+        <v>0.03611816776722611</v>
       </c>
       <c r="F9" t="n">
-        <v>3.803318886386638</v>
+        <v>3.611816776722611</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.80%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2618,19 +2618,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대표자불일치여부</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03769171190310019</v>
+        <v>0.03477271178468273</v>
       </c>
       <c r="F10" t="n">
-        <v>3.769171190310014</v>
+        <v>3.477271178468274</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=3.77%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2654,19 +2654,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03669786363562316</v>
+        <v>0.0344039068366</v>
       </c>
       <c r="F11" t="n">
-        <v>3.669786363562311</v>
+        <v>3.44039068366</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.44%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2746,19 +2746,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2354919926285472</v>
+        <v>0.2770684556012389</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06181358361811956</v>
+        <v>0.0551125459600037</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=27.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2782,19 +2782,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1389882420120957</v>
+        <v>0.1703274904421835</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03648260488033528</v>
+        <v>0.03388036947358997</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=13.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=17.03%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2818,19 +2818,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1307135255794641</v>
+        <v>0.1166684700281321</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03431059949528809</v>
+        <v>0.02320688727468401</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=13.07%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=11.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2854,19 +2854,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.09743296908661454</v>
+        <v>0.1080844694510566</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02557488649432327</v>
+        <v>0.02149941709263758</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=9.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=10.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2890,19 +2890,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.09413657954162016</v>
+        <v>0.09138534227800571</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02470962713453345</v>
+        <v>0.01817774190655552</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=9.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.14%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2926,19 +2926,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.09272458276014207</v>
+        <v>0.06511938252903433</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02433899635364706</v>
+        <v>0.01295309837682734</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=9.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2962,19 +2962,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.07495003504036123</v>
+        <v>0.06332503787059059</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01967340887660712</v>
+        <v>0.01259617971482385</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=7.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=6.33%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.05975030498092234</v>
+        <v>0.040269061530693</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01568367752941874</v>
+        <v>0.008010043942247358</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.98%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.03%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3034,19 +3034,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.02560282399356293</v>
+        <v>0.02744716150905338</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006720408129895161</v>
+        <v>0.00545960003587137</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=2.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=2.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3070,19 +3070,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TMNT_INDV_BZR_CLT_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>당월개인사업자거래처수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.009094920445401911</v>
+        <v>0.01709586669552097</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002387298265120907</v>
+        <v>0.00340059187516828</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 당월개인사업자거래처수(TMNT_INDV_BZR_CLT_NUM). 기여도(정규화 비중)=0.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=1.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.3551872132603224</v>
+        <v>0.2989836767503042</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09156760468956948</v>
+        <v>0.06737871042955795</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=35.52%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=29.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1210067866128246</v>
+        <v>0.1900691609165165</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03119566580004468</v>
+        <v>0.04283382656264023</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=12.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=19.01%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3234,19 +3234,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.09550941880378003</v>
+        <v>0.1094318299389545</v>
       </c>
       <c r="F4" t="n">
-        <v>0.024622419891972</v>
+        <v>0.02466146533943159</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=9.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=10.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3270,19 +3270,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.08317300577179218</v>
+        <v>0.09961877929788324</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02144208076480753</v>
+        <v>0.02245000448390294</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=8.32%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=9.96%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3306,19 +3306,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0470834478530202</v>
+        <v>0.0671473708505427</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01213815807402807</v>
+        <v>0.01513227513227527</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3342,19 +3342,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04409184126514275</v>
+        <v>0.04746555881861263</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01136691902262477</v>
+        <v>0.01069679849340871</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3378,19 +3378,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04333072580815647</v>
+        <v>0.03771617760586961</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01117070272686144</v>
+        <v>0.008499686126804851</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.33%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.77%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3414,19 +3414,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03891202773842957</v>
+        <v>0.03252711919712811</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01003155812090184</v>
+        <v>0.007330284279436938</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.89%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=3.25%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3450,19 +3450,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03607898687075828</v>
+        <v>0.01931571281904346</v>
       </c>
       <c r="F10" t="n">
-        <v>0.009301197464449407</v>
+        <v>0.004352972827549206</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=3.61%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=1.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3486,19 +3486,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.01897503118459181</v>
+        <v>0.01564676201163554</v>
       </c>
       <c r="F11" t="n">
-        <v>0.004891781262433892</v>
+        <v>0.003526141153259887</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=1.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=1.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0700729582360157</v>
+        <v>0.07123498568589968</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0700729582360157</v>
+        <v>0.07123498568589968</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.01%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06148273354766497</v>
+        <v>0.06438996081869364</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06148273354766497</v>
+        <v>0.06438996081869364</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.15%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.44%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05878294907501541</v>
+        <v>0.05839048873031386</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05878294907501541</v>
+        <v>0.05839048873031386</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.88%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3686,19 +3686,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05384256859475585</v>
+        <v>0.05427018714487944</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05384256859475585</v>
+        <v>0.05427018714487944</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.38%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.43%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0527039178199459</v>
+        <v>0.05358114621860463</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0527039178199459</v>
+        <v>0.05358114621860463</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.27%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3758,19 +3758,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04792607095040281</v>
+        <v>0.05098330684009479</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04792607095040281</v>
+        <v>0.05098330684009479</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.79%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.10%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3794,19 +3794,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04662512948148972</v>
+        <v>0.04893369782155989</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04662512948148972</v>
+        <v>0.04893369782155989</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.66%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04540918801236458</v>
+        <v>0.04303240847945023</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04540918801236458</v>
+        <v>0.04303240847945023</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.54%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3875,10 +3875,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03300190271002322</v>
+        <v>0.03644836213775499</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03300190271002322</v>
+        <v>0.03644836213775499</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.64%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3902,19 +3902,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03110928199837388</v>
+        <v>0.02993899235451626</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03110928199837388</v>
+        <v>0.02993899235451626</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.11%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3994,19 +3994,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1703765778033789</v>
+        <v>0.1027335695024538</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01773032250328394</v>
+        <v>0.006969778495202472</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=17.04%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=10.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4030,19 +4030,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1219556905672209</v>
+        <v>0.09652091154231966</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01269137901902762</v>
+        <v>0.006548291633037551</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=12.20%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=9.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4066,19 +4066,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.08969255748179694</v>
+        <v>0.07809443240098939</v>
       </c>
       <c r="F4" t="n">
-        <v>0.009333900180409971</v>
+        <v>0.005298179535467795</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=8.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4102,19 +4102,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.07269679987429753</v>
+        <v>0.06968751652302239</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00756522829220968</v>
+        <v>0.00472782710070857</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=7.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4138,19 +4138,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>지자체수행보조사업수</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05321321950452901</v>
+        <v>0.05950933220535835</v>
       </c>
       <c r="F6" t="n">
-        <v>0.005537659902654923</v>
+        <v>0.004037306071204505</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=5.32%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4174,19 +4174,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05130152411878593</v>
+        <v>0.05448633215248471</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005338718380561547</v>
+        <v>0.003696529459241427</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.13%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4210,19 +4210,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LBST_EXE_SUM_AMT</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>인건비집행합계금액</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04928507830094729</v>
+        <v>0.04909321630624239</v>
       </c>
       <c r="F8" t="n">
-        <v>0.005128875953147982</v>
+        <v>0.003330642991660082</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비집행합계금액(LBST_EXE_SUM_AMT). 기여도(정규화 비중)=4.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4246,19 +4246,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04705913161891651</v>
+        <v>0.04446676888912223</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00489723171509393</v>
+        <v>0.003016769796430951</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=4.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4282,19 +4282,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.04588068925784221</v>
+        <v>0.03666790038597665</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00477459653024187</v>
+        <v>0.002487669267330406</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=4.59%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4318,19 +4318,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>보조금전용신용카드집행건수</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.04224061174252269</v>
+        <v>0.0365357161740591</v>
       </c>
       <c r="F11" t="n">
-        <v>0.004395790070365391</v>
+        <v>0.002478701461752442</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.22%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=3.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/comparison/feature_importance_top10_all.xlsx
+++ b/outputs/reports/comparison/feature_importance_top10_all.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="전체TOP10(all)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="catboost" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="easy_ensemble" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="gradient_boosting" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="random_forest" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="stacked_ensemble" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체TOP10(all)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catboost_v1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="easy_ensemble_v1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gradient_boosting_v1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_forest_v1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stacked_ensemble_v1" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,24 +469,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.06671461789117154</v>
+        <v>0.0720834366819162</v>
       </c>
       <c r="F2" t="n">
-        <v>6.671461789117155</v>
+        <v>7.208343668191625</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -495,7 +495,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.21%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -505,24 +505,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06495441989195058</v>
+        <v>0.06054513955043873</v>
       </c>
       <c r="F3" t="n">
-        <v>6.495441989195059</v>
+        <v>6.054513955043876</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.05%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -541,24 +541,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05547755973096497</v>
+        <v>0.05896145497730271</v>
       </c>
       <c r="F4" t="n">
-        <v>5.547755973096498</v>
+        <v>5.896145497730275</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -567,7 +567,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.55%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.90%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -577,24 +577,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05417814811546744</v>
+        <v>0.05096941996978932</v>
       </c>
       <c r="F5" t="n">
-        <v>5.417814811546745</v>
+        <v>5.096941996978935</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=5.10%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -613,24 +613,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05058522443296955</v>
+        <v>0.04933380106314258</v>
       </c>
       <c r="F6" t="n">
-        <v>5.058522443296956</v>
+        <v>4.933380106314261</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.93%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -649,24 +649,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04458071949171321</v>
+        <v>0.04914549675775322</v>
       </c>
       <c r="F7" t="n">
-        <v>4.458071949171321</v>
+        <v>4.914549675775325</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.46%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.91%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -685,24 +685,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04060187085898578</v>
+        <v>0.04751753225903853</v>
       </c>
       <c r="F8" t="n">
-        <v>4.060187085898579</v>
+        <v>4.751753225903856</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=4.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -721,24 +721,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03611816776722611</v>
+        <v>0.04720868290349021</v>
       </c>
       <c r="F9" t="n">
-        <v>3.611816776722611</v>
+        <v>4.720868290349023</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.72%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -757,24 +757,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03477271178468273</v>
+        <v>0.04484785765179874</v>
       </c>
       <c r="F10" t="n">
-        <v>3.477271178468274</v>
+        <v>4.484785765179876</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -793,24 +793,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0344039068366</v>
+        <v>0.03747459357124595</v>
       </c>
       <c r="F11" t="n">
-        <v>3.44039068366</v>
+        <v>3.747459357124598</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.44%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -829,24 +829,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.1027335695024538</v>
+        <v>0.1781127861529395</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006969778495202472</v>
+        <v>0.0008332288532263421</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=10.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=17.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -865,24 +865,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09652091154231966</v>
+        <v>0.09715242881070832</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006548291633037551</v>
+        <v>0.0004544884653962522</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=9.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=9.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -901,24 +901,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.07809443240098939</v>
+        <v>0.09659408151866568</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005298179535467795</v>
+        <v>0.0004518764627214344</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=9.66%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -937,24 +937,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.06968751652302239</v>
+        <v>0.08096035734221936</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00472782710070857</v>
+        <v>0.0003787403878300344</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=8.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -973,24 +973,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>지자체수행보조사업수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.05950933220535835</v>
+        <v>0.07146845337799287</v>
       </c>
       <c r="F16" t="n">
-        <v>0.004037306071204505</v>
+        <v>0.0003343363423604639</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=7.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1009,24 +1009,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.05448633215248471</v>
+        <v>0.04578447794526556</v>
       </c>
       <c r="F17" t="n">
-        <v>0.003696529459241427</v>
+        <v>0.0002141842193246202</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.58%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1045,24 +1045,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.04909321630624239</v>
+        <v>0.03852596314907911</v>
       </c>
       <c r="F18" t="n">
-        <v>0.003330642991660082</v>
+        <v>0.0001802281845537101</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=3.85%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1081,24 +1081,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.04446676888912223</v>
+        <v>0.03740926856505316</v>
       </c>
       <c r="F19" t="n">
-        <v>0.003016769796430951</v>
+        <v>0.0001750041792043522</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=4.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=3.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1117,24 +1117,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>지자체수행보조사업수</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.03666790038597665</v>
+        <v>0.03629257398101535</v>
       </c>
       <c r="F20" t="n">
-        <v>0.002487669267330406</v>
+        <v>0.0001697801738549387</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.63%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1153,24 +1153,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>보조금전용신용카드집행건수</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0365357161740591</v>
+        <v>0.0351758793969894</v>
       </c>
       <c r="F21" t="n">
-        <v>0.002478701461752442</v>
+        <v>0.0001645561685055807</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=3.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.52%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1203,10 +1203,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.2770684556012389</v>
+        <v>0.2562100699289994</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0551125459600037</v>
+        <v>0.08751776161818792</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=27.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=25.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1225,24 +1225,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.1703274904421835</v>
+        <v>0.1949562418037012</v>
       </c>
       <c r="F23" t="n">
-        <v>0.03388036947358997</v>
+        <v>0.06659431419257783</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=17.03%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=19.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1261,24 +1261,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.1166684700281321</v>
+        <v>0.1093935790725324</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02320688727468401</v>
+        <v>0.03736731026412576</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=11.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=10.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1297,24 +1297,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.1080844694510566</v>
+        <v>0.0834101188678308</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02149941709263758</v>
+        <v>0.02849172517552673</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=10.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=8.34%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1333,24 +1333,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.09138534227800571</v>
+        <v>0.07228800501623002</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01817774190655552</v>
+        <v>0.02469256728518898</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.14%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1369,24 +1369,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.06511938252903433</v>
+        <v>0.07008575765338301</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01295309837682734</v>
+        <v>0.02394031051487805</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=7.01%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1405,24 +1405,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.06332503787059059</v>
+        <v>0.06775733986870594</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01259617971482385</v>
+        <v>0.02314495570043462</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=6.33%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1441,24 +1441,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.040269061530693</v>
+        <v>0.05602349063853686</v>
       </c>
       <c r="F29" t="n">
-        <v>0.008010043942247358</v>
+        <v>0.01913683759612173</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.03%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.60%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1477,24 +1477,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_DSCRD_YN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자불일치여부</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.02744716150905338</v>
+        <v>0.03345427851547132</v>
       </c>
       <c r="F30" t="n">
-        <v>0.00545960003587137</v>
+        <v>0.01142751170177209</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=2.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=3.35%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1513,24 +1513,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.01709586669552097</v>
+        <v>0.0253984882489458</v>
       </c>
       <c r="F31" t="n">
-        <v>0.00340059187516828</v>
+        <v>0.008675766883985359</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=1.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=2.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1549,24 +1549,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.2989836767503042</v>
+        <v>0.1725924154968874</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06737871042955795</v>
+        <v>0.03959796054831155</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=29.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=17.26%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1585,24 +1585,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.1900691609165165</v>
+        <v>0.1514851372428482</v>
       </c>
       <c r="F33" t="n">
-        <v>0.04283382656264023</v>
+        <v>0.03475530758943485</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=19.01%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=15.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1621,24 +1621,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.1094318299389545</v>
+        <v>0.1492537313432844</v>
       </c>
       <c r="F34" t="n">
-        <v>0.02466146533943159</v>
+        <v>0.03424335506519549</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=10.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=14.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1657,24 +1657,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.09961877929788324</v>
+        <v>0.1108872115395569</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02245000448390294</v>
+        <v>0.02544090605148774</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=9.96%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=11.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1693,24 +1693,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.0671473708505427</v>
+        <v>0.1016428156699347</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01513227513227527</v>
+        <v>0.02331995987963886</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=10.16%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1729,24 +1729,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_DSCRD_YN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자불일치여부</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.04746555881861263</v>
+        <v>0.07307854321072019</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01069679849340871</v>
+        <v>0.01676644516883979</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=7.31%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1779,10 +1779,10 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.03771617760586961</v>
+        <v>0.05602422669262386</v>
       </c>
       <c r="F38" t="n">
-        <v>0.008499686126804851</v>
+        <v>0.01285366516215303</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.77%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.60%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1801,24 +1801,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.03252711919712811</v>
+        <v>0.04550474173753693</v>
       </c>
       <c r="F39" t="n">
-        <v>0.007330284279436938</v>
+        <v>0.01044017469073888</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=3.25%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1837,24 +1837,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.01931571281904346</v>
+        <v>0.02871227387092019</v>
       </c>
       <c r="F40" t="n">
-        <v>0.004352972827549206</v>
+        <v>0.006587470745570034</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=1.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=2.87%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1873,24 +1873,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.01564676201163554</v>
+        <v>0.02771041816091179</v>
       </c>
       <c r="F41" t="n">
-        <v>0.003526141153259887</v>
+        <v>0.006357614510197229</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=1.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=2.77%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.07123498568589968</v>
+        <v>0.0699099314364416</v>
       </c>
       <c r="F42" t="n">
-        <v>0.07123498568589968</v>
+        <v>0.0699099314364416</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=6.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.06438996081869364</v>
+        <v>0.06522771266272298</v>
       </c>
       <c r="F43" t="n">
-        <v>0.06438996081869364</v>
+        <v>0.06522771266272298</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.44%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.52%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.05839048873031386</v>
+        <v>0.06257466028351776</v>
       </c>
       <c r="F44" t="n">
-        <v>0.05839048873031386</v>
+        <v>0.06257466028351776</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.26%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.05427018714487944</v>
+        <v>0.05371746488869882</v>
       </c>
       <c r="F45" t="n">
-        <v>0.05427018714487944</v>
+        <v>0.05371746488869882</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.43%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.37%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2053,24 +2053,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.05358114621860463</v>
+        <v>0.05359413285871334</v>
       </c>
       <c r="F46" t="n">
-        <v>0.05358114621860463</v>
+        <v>0.05359413285871334</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2089,24 +2089,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.05098330684009479</v>
+        <v>0.05314864471147066</v>
       </c>
       <c r="F47" t="n">
-        <v>0.05098330684009479</v>
+        <v>0.05314864471147066</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.10%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.31%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.04893369782155989</v>
+        <v>0.05015250059614454</v>
       </c>
       <c r="F48" t="n">
-        <v>0.04893369782155989</v>
+        <v>0.05015250059614454</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.02%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.04303240847945023</v>
+        <v>0.04274640347258525</v>
       </c>
       <c r="F49" t="n">
-        <v>0.04303240847945023</v>
+        <v>0.04274640347258525</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.27%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.03644836213775499</v>
+        <v>0.03684917303412914</v>
       </c>
       <c r="F50" t="n">
-        <v>0.03644836213775499</v>
+        <v>0.03684917303412914</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.64%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.68%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.02993899235451626</v>
+        <v>0.02912809723430759</v>
       </c>
       <c r="F51" t="n">
-        <v>0.02993899235451626</v>
+        <v>0.02912809723430759</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.91%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2325,24 +2325,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.06671461789117154</v>
+        <v>0.0720834366819162</v>
       </c>
       <c r="F2" t="n">
-        <v>6.671461789117155</v>
+        <v>7.208343668191625</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.21%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2361,24 +2361,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06495441989195058</v>
+        <v>0.06054513955043873</v>
       </c>
       <c r="F3" t="n">
-        <v>6.495441989195059</v>
+        <v>6.054513955043876</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.05%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2397,24 +2397,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05547755973096497</v>
+        <v>0.05896145497730271</v>
       </c>
       <c r="F4" t="n">
-        <v>5.547755973096498</v>
+        <v>5.896145497730275</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.55%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.90%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2433,24 +2433,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05417814811546744</v>
+        <v>0.05096941996978932</v>
       </c>
       <c r="F5" t="n">
-        <v>5.417814811546745</v>
+        <v>5.096941996978935</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=5.10%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2469,24 +2469,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05058522443296955</v>
+        <v>0.04933380106314258</v>
       </c>
       <c r="F6" t="n">
-        <v>5.058522443296956</v>
+        <v>4.933380106314261</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.93%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2505,24 +2505,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04458071949171321</v>
+        <v>0.04914549675775322</v>
       </c>
       <c r="F7" t="n">
-        <v>4.458071949171321</v>
+        <v>4.914549675775325</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.46%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.91%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2541,24 +2541,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04060187085898578</v>
+        <v>0.04751753225903853</v>
       </c>
       <c r="F8" t="n">
-        <v>4.060187085898579</v>
+        <v>4.751753225903856</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=4.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2577,24 +2577,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03611816776722611</v>
+        <v>0.04720868290349021</v>
       </c>
       <c r="F9" t="n">
-        <v>3.611816776722611</v>
+        <v>4.720868290349023</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.72%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2613,24 +2613,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03477271178468273</v>
+        <v>0.04484785765179874</v>
       </c>
       <c r="F10" t="n">
-        <v>3.477271178468274</v>
+        <v>4.484785765179876</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2649,24 +2649,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>catboost</t>
+          <t>catboost_v1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0344039068366</v>
+        <v>0.03747459357124595</v>
       </c>
       <c r="F11" t="n">
-        <v>3.44039068366</v>
+        <v>3.747459357124598</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.44%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2770684556012389</v>
+        <v>0.2562100699289994</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0551125459600037</v>
+        <v>0.08751776161818792</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=27.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=25.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2777,24 +2777,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1703274904421835</v>
+        <v>0.1949562418037012</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03388036947358997</v>
+        <v>0.06659431419257783</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=17.03%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=19.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2813,24 +2813,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1166684700281321</v>
+        <v>0.1093935790725324</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02320688727468401</v>
+        <v>0.03736731026412576</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=11.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=10.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2849,24 +2849,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.1080844694510566</v>
+        <v>0.0834101188678308</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02149941709263758</v>
+        <v>0.02849172517552673</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=10.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=8.34%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2885,24 +2885,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.09138534227800571</v>
+        <v>0.07228800501623002</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01817774190655552</v>
+        <v>0.02469256728518898</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.14%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2921,24 +2921,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.06511938252903433</v>
+        <v>0.07008575765338301</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01295309837682734</v>
+        <v>0.02394031051487805</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=7.01%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2957,24 +2957,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.06332503787059059</v>
+        <v>0.06775733986870594</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01259617971482385</v>
+        <v>0.02314495570043462</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=6.33%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2993,24 +2993,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.040269061530693</v>
+        <v>0.05602349063853686</v>
       </c>
       <c r="F9" t="n">
-        <v>0.008010043942247358</v>
+        <v>0.01913683759612173</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.03%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.60%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3029,24 +3029,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_DSCRD_YN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자불일치여부</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.02744716150905338</v>
+        <v>0.03345427851547132</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00545960003587137</v>
+        <v>0.01142751170177209</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=2.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=3.35%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3065,24 +3065,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>easy_ensemble</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.01709586669552097</v>
+        <v>0.0253984882489458</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00340059187516828</v>
+        <v>0.008675766883985359</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=1.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=2.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3157,24 +3157,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2989836767503042</v>
+        <v>0.1725924154968874</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06737871042955795</v>
+        <v>0.03959796054831155</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=29.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=17.26%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3193,24 +3193,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1900691609165165</v>
+        <v>0.1514851372428482</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04283382656264023</v>
+        <v>0.03475530758943485</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=19.01%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=15.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3229,24 +3229,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1094318299389545</v>
+        <v>0.1492537313432844</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02466146533943159</v>
+        <v>0.03424335506519549</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=10.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=14.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3265,24 +3265,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.09961877929788324</v>
+        <v>0.1108872115395569</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02245000448390294</v>
+        <v>0.02544090605148774</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=9.96%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=11.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3301,24 +3301,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0671473708505427</v>
+        <v>0.1016428156699347</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01513227513227527</v>
+        <v>0.02331995987963886</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=10.16%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3337,24 +3337,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_DSCRD_YN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자불일치여부</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04746555881861263</v>
+        <v>0.07307854321072019</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01069679849340871</v>
+        <v>0.01676644516883979</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=7.31%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.03771617760586961</v>
+        <v>0.05602422669262386</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008499686126804851</v>
+        <v>0.01285366516215303</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.77%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.60%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3409,24 +3409,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03252711919712811</v>
+        <v>0.04550474173753693</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007330284279436938</v>
+        <v>0.01044017469073888</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=3.25%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3445,24 +3445,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.01931571281904346</v>
+        <v>0.02871227387092019</v>
       </c>
       <c r="F10" t="n">
-        <v>0.004352972827549206</v>
+        <v>0.006587470745570034</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=1.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=2.87%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3481,24 +3481,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gradient_boosting</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.01564676201163554</v>
+        <v>0.02771041816091179</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003526141153259887</v>
+        <v>0.006357614510197229</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=1.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=2.77%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07123498568589968</v>
+        <v>0.0699099314364416</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07123498568589968</v>
+        <v>0.0699099314364416</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=6.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3623,10 +3623,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06438996081869364</v>
+        <v>0.06522771266272298</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06438996081869364</v>
+        <v>0.06522771266272298</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.44%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.52%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05839048873031386</v>
+        <v>0.06257466028351776</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05839048873031386</v>
+        <v>0.06257466028351776</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.26%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05427018714487944</v>
+        <v>0.05371746488869882</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05427018714487944</v>
+        <v>0.05371746488869882</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.43%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.37%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3717,24 +3717,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05358114621860463</v>
+        <v>0.05359413285871334</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05358114621860463</v>
+        <v>0.05359413285871334</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3753,24 +3753,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05098330684009479</v>
+        <v>0.05314864471147066</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05098330684009479</v>
+        <v>0.05314864471147066</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.10%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.31%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3789,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04893369782155989</v>
+        <v>0.05015250059614454</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04893369782155989</v>
+        <v>0.05015250059614454</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.02%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04303240847945023</v>
+        <v>0.04274640347258525</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04303240847945023</v>
+        <v>0.04274640347258525</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.27%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3875,10 +3875,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03644836213775499</v>
+        <v>0.03684917303412914</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03644836213775499</v>
+        <v>0.03684917303412914</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.64%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.68%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>random_forest</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3911,10 +3911,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02993899235451626</v>
+        <v>0.02912809723430759</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02993899235451626</v>
+        <v>0.02912809723430759</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.91%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3989,24 +3989,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1027335695024538</v>
+        <v>0.1781127861529395</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006969778495202472</v>
+        <v>0.0008332288532263421</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=10.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=17.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4025,24 +4025,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.09652091154231966</v>
+        <v>0.09715242881070832</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006548291633037551</v>
+        <v>0.0004544884653962522</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=9.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=9.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4061,24 +4061,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.07809443240098939</v>
+        <v>0.09659408151866568</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005298179535467795</v>
+        <v>0.0004518764627214344</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=9.66%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4097,24 +4097,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.06968751652302239</v>
+        <v>0.08096035734221936</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00472782710070857</v>
+        <v>0.0003787403878300344</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=8.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4133,24 +4133,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지자체수행보조사업수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05950933220535835</v>
+        <v>0.07146845337799287</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004037306071204505</v>
+        <v>0.0003343363423604639</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=7.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4169,24 +4169,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05448633215248471</v>
+        <v>0.04578447794526556</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003696529459241427</v>
+        <v>0.0002141842193246202</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.58%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4205,24 +4205,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04909321630624239</v>
+        <v>0.03852596314907911</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003330642991660082</v>
+        <v>0.0001802281845537101</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=3.85%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4241,24 +4241,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04446676888912223</v>
+        <v>0.03740926856505316</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003016769796430951</v>
+        <v>0.0001750041792043522</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=4.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=3.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4277,24 +4277,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>지자체수행보조사업수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03666790038597665</v>
+        <v>0.03629257398101535</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002487669267330406</v>
+        <v>0.0001697801738549387</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.63%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4313,24 +4313,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>stacked_ensemble</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>보조금전용신용카드집행건수</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0365357161740591</v>
+        <v>0.0351758793969894</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002478701461752442</v>
+        <v>0.0001645561685055807</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=3.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.52%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/comparison/feature_importance_top10_all.xlsx
+++ b/outputs/reports/comparison/feature_importance_top10_all.xlsx
@@ -9,10 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체TOP10(all)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catboost_v1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="easy_ensemble_v1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gradient_boosting_v1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_forest_v1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stacked_ensemble_v1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catboost_v2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_forest_v1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_forest_v2" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,10 +482,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0720834366819162</v>
+        <v>0.06512370292287779</v>
       </c>
       <c r="F2" t="n">
-        <v>7.208343668191625</v>
+        <v>6.512370292287774</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -495,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.21%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.51%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -519,10 +518,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06054513955043873</v>
+        <v>0.06218461134590617</v>
       </c>
       <c r="F3" t="n">
-        <v>6.054513955043876</v>
+        <v>6.218461134590611</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -531,7 +530,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.05%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.22%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -555,10 +554,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05896145497730271</v>
+        <v>0.0586404025870892</v>
       </c>
       <c r="F4" t="n">
-        <v>5.896145497730275</v>
+        <v>5.864040258708916</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -567,7 +566,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.90%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.86%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -582,19 +581,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지자체대비보조사업금액비율</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05096941996978932</v>
+        <v>0.04820782632383652</v>
       </c>
       <c r="F5" t="n">
-        <v>5.096941996978935</v>
+        <v>4.820782632383648</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -603,7 +602,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=5.10%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.82%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -618,19 +617,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04933380106314258</v>
+        <v>0.04747477439020054</v>
       </c>
       <c r="F6" t="n">
-        <v>4.933380106314261</v>
+        <v>4.74747743902005</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -639,7 +638,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.93%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -663,10 +662,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04914549675775322</v>
+        <v>0.04480735044966697</v>
       </c>
       <c r="F7" t="n">
-        <v>4.914549675775325</v>
+        <v>4.480735044966694</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -675,7 +674,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.91%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -690,19 +689,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04751753225903853</v>
+        <v>0.04033593740657232</v>
       </c>
       <c r="F8" t="n">
-        <v>4.751753225903856</v>
+        <v>4.033593740657229</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -711,7 +710,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=4.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.03%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -726,19 +725,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04720868290349021</v>
+        <v>0.03634252123369216</v>
       </c>
       <c r="F9" t="n">
-        <v>4.720868290349023</v>
+        <v>3.634252123369213</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -747,7 +746,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.72%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.63%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -762,19 +761,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.04484785765179874</v>
+        <v>0.03377831181233264</v>
       </c>
       <c r="F10" t="n">
-        <v>4.484785765179876</v>
+        <v>3.377831181233262</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -783,7 +782,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=3.38%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -798,19 +797,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03747459357124595</v>
+        <v>0.03369229173308515</v>
       </c>
       <c r="F11" t="n">
-        <v>3.747459357124598</v>
+        <v>3.369229173308512</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -819,7 +818,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.37%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -829,7 +828,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>stacked_ensemble_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -843,19 +842,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.1781127861529395</v>
+        <v>0.07128537539281089</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0008332288532263421</v>
+        <v>0.07128537539281089</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=17.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.13%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -865,33 +864,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>stacked_ensemble_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09715242881070832</v>
+        <v>0.06794269690533204</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0004544884653962522</v>
+        <v>0.06794269690533204</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=9.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.79%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -901,33 +900,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>stacked_ensemble_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.09659408151866568</v>
+        <v>0.06032811954240906</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0004518764627214344</v>
+        <v>0.06032811954240906</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=9.66%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.03%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -937,33 +936,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>stacked_ensemble_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.08096035734221936</v>
+        <v>0.05352744284457885</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0003787403878300344</v>
+        <v>0.05352744284457885</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=8.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -973,33 +972,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>stacked_ensemble_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.07146845337799287</v>
+        <v>0.05347886914881447</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0003343363423604639</v>
+        <v>0.05347886914881447</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=7.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1009,33 +1008,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>stacked_ensemble_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.04578447794526556</v>
+        <v>0.05220979045101741</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0002141842193246202</v>
+        <v>0.05220979045101741</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.58%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.22%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1045,33 +1044,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>stacked_ensemble_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.03852596314907911</v>
+        <v>0.04822499703852008</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0001802281845537101</v>
+        <v>0.04822499703852008</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=3.85%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.82%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1081,33 +1080,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>stacked_ensemble_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.03740926856505316</v>
+        <v>0.04229378740443412</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0001750041792043522</v>
+        <v>0.04229378740443412</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=3.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1117,33 +1116,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>stacked_ensemble_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>지자체수행보조사업수</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.03629257398101535</v>
+        <v>0.03490214011419904</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0001697801738549387</v>
+        <v>0.03490214011419904</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.63%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.49%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1153,33 +1152,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>stacked_ensemble_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0351758793969894</v>
+        <v>0.02968403128616421</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0001645561685055807</v>
+        <v>0.02968403128616421</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.52%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.97%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1189,33 +1188,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.2562100699289994</v>
+        <v>0.07850951358445041</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08751776161818792</v>
+        <v>7.850951358445034</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=25.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.85%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -1225,33 +1224,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.1949562418037012</v>
+        <v>0.05953418487611781</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06659431419257783</v>
+        <v>5.953418487611776</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=19.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.95%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -1261,33 +1260,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.1093935790725324</v>
+        <v>0.05902799501884216</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03736731026412576</v>
+        <v>5.902799501884211</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=10.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.90%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -1297,33 +1296,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0834101188678308</v>
+        <v>0.05060763118691404</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02849172517552673</v>
+        <v>5.060763118691399</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=8.34%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -1333,33 +1332,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.07228800501623002</v>
+        <v>0.04418441392537081</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02469256728518898</v>
+        <v>4.418441392537077</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -1369,33 +1368,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.07008575765338301</v>
+        <v>0.04395703343026858</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02394031051487805</v>
+        <v>4.395703343026854</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=7.01%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.40%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -1405,33 +1404,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.06775733986870594</v>
+        <v>0.04225371024686373</v>
       </c>
       <c r="F28" t="n">
-        <v>0.02314495570043462</v>
+        <v>4.225371024686369</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.23%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -1441,33 +1440,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.05602349063853686</v>
+        <v>0.03613249857830451</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01913683759612173</v>
+        <v>3.613249857830448</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.60%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -1477,33 +1476,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>대표자불일치여부</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.03345427851547132</v>
+        <v>0.03327229716580977</v>
       </c>
       <c r="F30" t="n">
-        <v>0.01142751170177209</v>
+        <v>3.327229716580975</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=3.35%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.33%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -1513,33 +1512,33 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0253984882489458</v>
+        <v>0.03315060255846319</v>
       </c>
       <c r="F31" t="n">
-        <v>0.008675766883985359</v>
+        <v>3.315060255846316</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=2.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.32%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -1549,33 +1548,33 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.1725924154968874</v>
+        <v>0.07143149908118701</v>
       </c>
       <c r="F32" t="n">
-        <v>0.03959796054831155</v>
+        <v>0.07143149908118702</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=17.26%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.14%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1585,33 +1584,33 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.1514851372428482</v>
+        <v>0.0658730897024364</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03475530758943485</v>
+        <v>0.06587308970243641</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=15.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.59%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1620,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1635,19 +1634,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.1492537313432844</v>
+        <v>0.06240819698226026</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03424335506519549</v>
+        <v>0.06240819698226027</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=14.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.24%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1657,33 +1656,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.1108872115395569</v>
+        <v>0.05227164345278072</v>
       </c>
       <c r="F35" t="n">
-        <v>0.02544090605148774</v>
+        <v>0.05227164345278074</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=11.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1693,33 +1692,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.1016428156699347</v>
+        <v>0.05156726898647793</v>
       </c>
       <c r="F36" t="n">
-        <v>0.02331995987963886</v>
+        <v>0.05156726898647795</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=10.16%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.16%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1729,33 +1728,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>대표자불일치여부</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.07307854321072019</v>
+        <v>0.04990558558890892</v>
       </c>
       <c r="F37" t="n">
-        <v>0.01676644516883979</v>
+        <v>0.04990558558890893</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=7.31%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1764,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1779,19 +1778,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.05602422669262386</v>
+        <v>0.04772365960239108</v>
       </c>
       <c r="F38" t="n">
-        <v>0.01285366516215303</v>
+        <v>0.04772365960239109</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.60%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.77%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1801,33 +1800,33 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.04550474173753693</v>
+        <v>0.0428885918594519</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01044017469073888</v>
+        <v>0.04288859185945191</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.29%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1837,33 +1836,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.02871227387092019</v>
+        <v>0.03540480263418778</v>
       </c>
       <c r="F40" t="n">
-        <v>0.006587470745570034</v>
+        <v>0.03540480263418778</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=2.87%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.54%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1873,393 +1872,33 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.02771041816091179</v>
+        <v>0.02928295777591394</v>
       </c>
       <c r="F41" t="n">
-        <v>0.006357614510197229</v>
+        <v>0.02928295777591394</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=2.77%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>random_forest_v1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>LAF_CD</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>지방자치단체코드</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>0.0699099314364416</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.0699099314364416</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>tree_impurity</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=6.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>2</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>random_forest_v1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>DEPT_CD</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>부서코드</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>0.06522771266272298</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.06522771266272298</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>tree_impurity</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.52%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>3</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>random_forest_v1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>AID_BZR_CAP_CD</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>보조사업자시도코드</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>0.06257466028351776</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.06257466028351776</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>tree_impurity</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.26%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>4</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>random_forest_v1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>RPRSV_AGGP_DV_CD</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>대표자연령대구분코드</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>0.05371746488869882</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.05371746488869882</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>tree_impurity</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.37%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>5</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>random_forest_v1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>RPRSV_HSHD_DV_CD</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>대표자세대구분코드</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>0.05359413285871334</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.05359413285871334</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>tree_impurity</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>6</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>random_forest_v1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>FTEP_STF_NUM</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>상근직원수</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>0.05314864471147066</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.05314864471147066</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>tree_impurity</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.31%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>7</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>random_forest_v1</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>MBR_NUM</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>회원수</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>0.05015250059614454</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.05015250059614454</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>tree_impurity</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.02%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>8</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>random_forest_v1</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>AID_BZR_FNDN_YS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>보조사업자설립년수</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>0.04274640347258525</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.04274640347258525</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>tree_impurity</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.27%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>9</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>random_forest_v1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>SECT_CD</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>부문코드</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>0.03684917303412914</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.03684917303412914</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>tree_impurity</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.68%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>10</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>random_forest_v1</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>BIZCT_SBAT_AMT</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>사업비보조금금액</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>0.02912809723430759</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.02912809723430759</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>tree_impurity</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.91%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.93%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2339,10 +1978,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0720834366819162</v>
+        <v>0.06512370292287779</v>
       </c>
       <c r="F2" t="n">
-        <v>7.208343668191625</v>
+        <v>6.512370292287774</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2351,7 +1990,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.21%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.51%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2375,10 +2014,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06054513955043873</v>
+        <v>0.06218461134590617</v>
       </c>
       <c r="F3" t="n">
-        <v>6.054513955043876</v>
+        <v>6.218461134590611</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2387,7 +2026,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.05%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.22%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2411,10 +2050,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05896145497730271</v>
+        <v>0.0586404025870892</v>
       </c>
       <c r="F4" t="n">
-        <v>5.896145497730275</v>
+        <v>5.864040258708916</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2423,7 +2062,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.90%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.86%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2438,19 +2077,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지자체대비보조사업금액비율</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05096941996978932</v>
+        <v>0.04820782632383652</v>
       </c>
       <c r="F5" t="n">
-        <v>5.096941996978935</v>
+        <v>4.820782632383648</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2459,7 +2098,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=5.10%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.82%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2474,19 +2113,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04933380106314258</v>
+        <v>0.04747477439020054</v>
       </c>
       <c r="F6" t="n">
-        <v>4.933380106314261</v>
+        <v>4.74747743902005</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2495,7 +2134,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.93%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2519,10 +2158,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04914549675775322</v>
+        <v>0.04480735044966697</v>
       </c>
       <c r="F7" t="n">
-        <v>4.914549675775325</v>
+        <v>4.480735044966694</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2531,7 +2170,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.91%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2546,19 +2185,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04751753225903853</v>
+        <v>0.04033593740657232</v>
       </c>
       <c r="F8" t="n">
-        <v>4.751753225903856</v>
+        <v>4.033593740657229</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2567,7 +2206,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=4.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.03%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2582,19 +2221,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04720868290349021</v>
+        <v>0.03634252123369216</v>
       </c>
       <c r="F9" t="n">
-        <v>4.720868290349023</v>
+        <v>3.634252123369213</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2603,7 +2242,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.72%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.63%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2618,19 +2257,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.04484785765179874</v>
+        <v>0.03377831181233264</v>
       </c>
       <c r="F10" t="n">
-        <v>4.484785765179876</v>
+        <v>3.377831181233262</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2639,7 +2278,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=3.38%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2654,19 +2293,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03747459357124595</v>
+        <v>0.03369229173308515</v>
       </c>
       <c r="F11" t="n">
-        <v>3.747459357124598</v>
+        <v>3.369229173308512</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2675,7 +2314,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.37%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2741,33 +2380,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2562100699289994</v>
+        <v>0.07850951358445041</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08751776161818792</v>
+        <v>7.850951358445034</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=25.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.85%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2777,33 +2416,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1949562418037012</v>
+        <v>0.05953418487611781</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06659431419257783</v>
+        <v>5.953418487611776</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=19.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.95%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2813,33 +2452,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1093935790725324</v>
+        <v>0.05902799501884216</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03736731026412576</v>
+        <v>5.902799501884211</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=10.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.90%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2849,33 +2488,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0834101188678308</v>
+        <v>0.05060763118691404</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02849172517552673</v>
+        <v>5.060763118691399</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=8.34%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2885,33 +2524,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.07228800501623002</v>
+        <v>0.04418441392537081</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02469256728518898</v>
+        <v>4.418441392537077</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2921,33 +2560,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.07008575765338301</v>
+        <v>0.04395703343026858</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02394031051487805</v>
+        <v>4.395703343026854</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=7.01%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.40%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2957,33 +2596,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.06775733986870594</v>
+        <v>0.04225371024686373</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02314495570043462</v>
+        <v>4.225371024686369</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.23%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2993,33 +2632,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.05602349063853686</v>
+        <v>0.03613249857830451</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01913683759612173</v>
+        <v>3.613249857830448</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.60%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -3029,33 +2668,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대표자불일치여부</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03345427851547132</v>
+        <v>0.03327229716580977</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01142751170177209</v>
+        <v>3.327229716580975</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=3.35%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.33%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -3065,33 +2704,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>easy_ensemble_v1</t>
+          <t>catboost_v2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0253984882489458</v>
+        <v>0.03315060255846319</v>
       </c>
       <c r="F11" t="n">
-        <v>0.008675766883985359</v>
+        <v>3.315060255846316</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>catboost_prediction</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=2.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.32%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -3157,33 +2796,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1725924154968874</v>
+        <v>0.07128537539281089</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03959796054831155</v>
+        <v>0.07128537539281089</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=17.26%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.13%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3193,33 +2832,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1514851372428482</v>
+        <v>0.06794269690533204</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03475530758943485</v>
+        <v>0.06794269690533204</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=15.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.79%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3229,7 +2868,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3243,19 +2882,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1492537313432844</v>
+        <v>0.06032811954240906</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03424335506519549</v>
+        <v>0.06032811954240906</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=14.93%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.03%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3265,33 +2904,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.1108872115395569</v>
+        <v>0.05352744284457885</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02544090605148774</v>
+        <v>0.05352744284457885</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=11.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3301,33 +2940,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.1016428156699347</v>
+        <v>0.05347886914881447</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02331995987963886</v>
+        <v>0.05347886914881447</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=10.16%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3337,33 +2976,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자불일치여부</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.07307854321072019</v>
+        <v>0.05220979045101741</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01676644516883979</v>
+        <v>0.05220979045101741</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=7.31%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.22%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3012,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3387,19 +3026,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.05602422669262386</v>
+        <v>0.04822499703852008</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01285366516215303</v>
+        <v>0.04822499703852008</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.60%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.82%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3409,33 +3048,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04550474173753693</v>
+        <v>0.04229378740443412</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01044017469073888</v>
+        <v>0.04229378740443412</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3445,33 +3084,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.02871227387092019</v>
+        <v>0.03490214011419904</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006587470745570034</v>
+        <v>0.03490214011419904</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=2.87%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.49%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3481,33 +3120,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>gradient_boosting_v1</t>
+          <t>random_forest_v1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02771041816091179</v>
+        <v>0.02968403128616421</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006357614510197229</v>
+        <v>0.02968403128616421</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>permutation_roc_auc</t>
+          <t>tree_impurity</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=2.77%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.97%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3573,7 +3212,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3587,10 +3226,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0699099314364416</v>
+        <v>0.07143149908118701</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0699099314364416</v>
+        <v>0.07143149908118702</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -3599,7 +3238,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=6.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.14%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3248,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3623,10 +3262,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06522771266272298</v>
+        <v>0.0658730897024364</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06522771266272298</v>
+        <v>0.06587308970243641</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -3635,7 +3274,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.52%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.59%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3284,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3659,10 +3298,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.06257466028351776</v>
+        <v>0.06240819698226026</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06257466028351776</v>
+        <v>0.06240819698226027</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -3671,7 +3310,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.26%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.24%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3320,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3695,10 +3334,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05371746488869882</v>
+        <v>0.05227164345278072</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05371746488869882</v>
+        <v>0.05227164345278074</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3707,7 +3346,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.37%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3356,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3731,10 +3370,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05359413285871334</v>
+        <v>0.05156726898647793</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05359413285871334</v>
+        <v>0.05156726898647795</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -3743,7 +3382,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.16%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3753,7 +3392,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3767,10 +3406,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05314864471147066</v>
+        <v>0.04990558558890892</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05314864471147066</v>
+        <v>0.04990558558890893</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -3779,7 +3418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.31%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3789,7 +3428,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3803,10 +3442,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.05015250059614454</v>
+        <v>0.04772365960239108</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05015250059614454</v>
+        <v>0.04772365960239109</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3815,7 +3454,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.02%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.77%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3464,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3839,10 +3478,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04274640347258525</v>
+        <v>0.0428885918594519</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04274640347258525</v>
+        <v>0.04288859185945191</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3851,7 +3490,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.27%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.29%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3500,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3875,10 +3514,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03684917303412914</v>
+        <v>0.03540480263418778</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03684917303412914</v>
+        <v>0.03540480263418778</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3887,7 +3526,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.68%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.54%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3897,24 +3536,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>random_forest_v2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02912809723430759</v>
+        <v>0.02928295777591394</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02912809723430759</v>
+        <v>0.02928295777591394</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3923,423 +3562,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.91%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>순위(rank)</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>알고리즘(algorithm)</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>피처명(feature)</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>피처명한글(feature_ko)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>기여도비중(importance_share)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>기여도원점수(importance_raw)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>측정방법(method)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>사유(reason)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>stacked_ensemble_v1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LAF_CD</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>지방자치단체코드</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.1781127861529395</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.0008332288532263421</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>permutation_roc_auc</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=17.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>stacked_ensemble_v1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>AID_BZR_CAP_CD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>보조사업자시도코드</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.09715242881070832</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.0004544884653962522</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>permutation_roc_auc</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=9.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>stacked_ensemble_v1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MBR_NUM</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>회원수</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.09659408151866568</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.0004518764627214344</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>permutation_roc_auc</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=9.66%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>stacked_ensemble_v1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>RPRSV_HSHD_DV_CD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>대표자세대구분코드</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.08096035734221936</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.0003787403878300344</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>permutation_roc_auc</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=8.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>stacked_ensemble_v1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DEPT_CD</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>부서코드</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.07146845337799287</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.0003343363423604639</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>permutation_roc_auc</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=7.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>stacked_ensemble_v1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AID_BZR_FNDN_YS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>보조사업자설립년수</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.04578447794526556</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.0002141842193246202</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>permutation_roc_auc</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.58%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>stacked_ensemble_v1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>FTEP_STF_NUM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>상근직원수</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.03852596314907911</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.0001802281845537101</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>permutation_roc_auc</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=3.85%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>stacked_ensemble_v1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>RPRSV_AGGP_DV_CD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>대표자연령대구분코드</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.03740926856505316</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0001750041792043522</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>permutation_roc_auc</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=3.74%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>stacked_ensemble_v1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>지자체수행보조사업수</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>0.03629257398101535</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.0001697801738549387</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>permutation_roc_auc</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.63%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>stacked_ensemble_v1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SECT_CD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>부문코드</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0351758793969894</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.0001645561685055807</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>permutation_roc_auc</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.52%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.93%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/comparison/feature_importance_top10_all.xlsx
+++ b/outputs/reports/comparison/feature_importance_top10_all.xlsx
@@ -10,8 +10,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체TOP10(all)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catboost_v1" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="catboost_v2" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_forest_v1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_forest_v2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="easy_ensemble_v1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="easy_ensemble_v2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gradient_boosting_v1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gradient_boosting_v2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_forest_v1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="random_forest_v2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stacked_ensemble_v1" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stacked_ensemble_v2" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,19 +479,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.06512370292287779</v>
+        <v>0.06671461789117154</v>
       </c>
       <c r="F2" t="n">
-        <v>6.512370292287774</v>
+        <v>6.671461789117155</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -494,7 +500,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.51%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -509,19 +515,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06218461134590617</v>
+        <v>0.06495441989195058</v>
       </c>
       <c r="F3" t="n">
-        <v>6.218461134590611</v>
+        <v>6.495441989195059</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -530,7 +536,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.22%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -545,19 +551,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0586404025870892</v>
+        <v>0.05547755973096497</v>
       </c>
       <c r="F4" t="n">
-        <v>5.864040258708916</v>
+        <v>5.547755973096498</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -566,7 +572,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.86%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.55%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -581,19 +587,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.04820782632383652</v>
+        <v>0.05417814811546744</v>
       </c>
       <c r="F5" t="n">
-        <v>4.820782632383648</v>
+        <v>5.417814811546745</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -602,7 +608,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.82%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -617,19 +623,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04747477439020054</v>
+        <v>0.05058522443296955</v>
       </c>
       <c r="F6" t="n">
-        <v>4.74747743902005</v>
+        <v>5.058522443296956</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -638,7 +644,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -653,19 +659,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04480735044966697</v>
+        <v>0.04458071949171321</v>
       </c>
       <c r="F7" t="n">
-        <v>4.480735044966694</v>
+        <v>4.458071949171321</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -674,7 +680,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.46%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -689,19 +695,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04033593740657232</v>
+        <v>0.04060187085898578</v>
       </c>
       <c r="F8" t="n">
-        <v>4.033593740657229</v>
+        <v>4.060187085898579</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -710,7 +716,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.03%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -725,19 +731,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03634252123369216</v>
+        <v>0.03611816776722611</v>
       </c>
       <c r="F9" t="n">
-        <v>3.634252123369213</v>
+        <v>3.611816776722611</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -746,7 +752,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.63%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -761,19 +767,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03377831181233264</v>
+        <v>0.03477271178468273</v>
       </c>
       <c r="F10" t="n">
-        <v>3.377831181233262</v>
+        <v>3.477271178468274</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -782,7 +788,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=3.38%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -797,19 +803,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03369229173308515</v>
+        <v>0.0344039068366</v>
       </c>
       <c r="F11" t="n">
-        <v>3.369229173308512</v>
+        <v>3.44039068366</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -818,7 +824,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.37%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.44%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -828,33 +834,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.07128537539281089</v>
+        <v>0.1027335695024538</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07128537539281089</v>
+        <v>0.006969778495202472</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.13%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=10.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -864,33 +870,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.06794269690533204</v>
+        <v>0.09652091154231966</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06794269690533204</v>
+        <v>0.006548291633037551</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.79%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=9.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -900,33 +906,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.06032811954240906</v>
+        <v>0.07809443240098939</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06032811954240906</v>
+        <v>0.005298179535467795</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.03%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -936,33 +942,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.05352744284457885</v>
+        <v>0.06968751652302239</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05352744284457885</v>
+        <v>0.00472782710070857</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -972,33 +978,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>지자체수행보조사업수</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.05347886914881447</v>
+        <v>0.05950933220535835</v>
       </c>
       <c r="F16" t="n">
-        <v>0.05347886914881447</v>
+        <v>0.004037306071204505</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1008,33 +1014,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.05220979045101741</v>
+        <v>0.05448633215248471</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05220979045101741</v>
+        <v>0.003696529459241427</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.22%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1044,33 +1050,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.04822499703852008</v>
+        <v>0.04909321630624239</v>
       </c>
       <c r="F18" t="n">
-        <v>0.04822499703852008</v>
+        <v>0.003330642991660082</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.82%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1080,33 +1086,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.04229378740443412</v>
+        <v>0.04446676888912223</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04229378740443412</v>
+        <v>0.003016769796430951</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=4.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1116,33 +1122,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.03490214011419904</v>
+        <v>0.03666790038597665</v>
       </c>
       <c r="F20" t="n">
-        <v>0.03490214011419904</v>
+        <v>0.002487669267330406</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.49%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1152,33 +1158,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>stacked_ensemble_v1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>보조금전용신용카드집행건수</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.02968403128616421</v>
+        <v>0.0365357161740591</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02968403128616421</v>
+        <v>0.002478701461752442</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.97%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=3.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1188,33 +1194,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>catboost_v2</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.07850951358445041</v>
+        <v>0.2369881283651408</v>
       </c>
       <c r="F22" t="n">
-        <v>7.850951358445034</v>
+        <v>0.05162945027351795</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>catboost_prediction</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.85%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1224,33 +1230,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>catboost_v2</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.05953418487611781</v>
+        <v>0.212956712166369</v>
       </c>
       <c r="F23" t="n">
-        <v>5.953418487611776</v>
+        <v>0.04639404537709613</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>catboost_prediction</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.95%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=21.30%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1260,33 +1266,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>catboost_v2</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.05902799501884216</v>
+        <v>0.1194243656661127</v>
       </c>
       <c r="F24" t="n">
-        <v>5.902799501884211</v>
+        <v>0.02601739754282112</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>catboost_prediction</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.90%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=11.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1296,33 +1302,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>catboost_v2</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.05060763118691404</v>
+        <v>0.0909143299359494</v>
       </c>
       <c r="F25" t="n">
-        <v>5.060763118691399</v>
+        <v>0.01980629539951562</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>catboost_prediction</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1332,33 +1338,33 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>catboost_v2</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.04418441392537081</v>
+        <v>0.07733439810317347</v>
       </c>
       <c r="F26" t="n">
-        <v>4.418441392537077</v>
+        <v>0.01684781633934174</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>catboost_prediction</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.73%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1368,33 +1374,33 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>catboost_v2</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.04395703343026858</v>
+        <v>0.05831261422949655</v>
       </c>
       <c r="F27" t="n">
-        <v>4.395703343026854</v>
+        <v>0.01270379338175942</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>catboost_prediction</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.40%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1404,33 +1410,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>catboost_v2</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.04225371024686373</v>
+        <v>0.04704197059259392</v>
       </c>
       <c r="F28" t="n">
-        <v>4.225371024686369</v>
+        <v>0.01024840821450984</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>catboost_prediction</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.23%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1440,33 +1446,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>catboost_v2</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>지자체대비보조사업금액비율</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.03613249857830451</v>
+        <v>0.04169891162959222</v>
       </c>
       <c r="F29" t="n">
-        <v>3.613249857830448</v>
+        <v>0.009084387050488751</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>catboost_prediction</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.17%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1476,33 +1482,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>catboost_v2</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.03327229716580977</v>
+        <v>0.03488218925460607</v>
       </c>
       <c r="F30" t="n">
-        <v>3.327229716580975</v>
+        <v>0.007599318446775971</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>catboost_prediction</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.33%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1512,33 +1518,33 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>catboost_v2</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.03315060255846319</v>
+        <v>0.03102925921657064</v>
       </c>
       <c r="F31" t="n">
-        <v>3.315060255846316</v>
+        <v>0.006759931844677491</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>catboost_prediction</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.32%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1548,33 +1554,33 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.07143149908118701</v>
+        <v>0.2662079403069144</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07143149908118702</v>
+        <v>0.05426239799121152</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.14%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=26.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1584,33 +1590,33 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0658730897024364</v>
+        <v>0.1355325214698025</v>
       </c>
       <c r="F33" t="n">
-        <v>0.06587308970243641</v>
+        <v>0.02762622186350999</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.59%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=13.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1620,33 +1626,33 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.06240819698226026</v>
+        <v>0.1189286217091377</v>
       </c>
       <c r="F34" t="n">
-        <v>0.06240819698226027</v>
+        <v>0.02424177203838218</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.24%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=11.89%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1656,33 +1662,33 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.05227164345278072</v>
+        <v>0.06474377023792785</v>
       </c>
       <c r="F35" t="n">
-        <v>0.05227164345278074</v>
+        <v>0.01319702268854805</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1692,33 +1698,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.05156726898647793</v>
+        <v>0.05747571448683674</v>
       </c>
       <c r="F36" t="n">
-        <v>0.05156726898647795</v>
+        <v>0.01171554120706658</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.16%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1728,33 +1734,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.04990558558890892</v>
+        <v>0.04826305786287505</v>
       </c>
       <c r="F37" t="n">
-        <v>0.04990558558890893</v>
+        <v>0.009837682719038621</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1764,33 +1770,33 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.04772365960239108</v>
+        <v>0.03557475714486848</v>
       </c>
       <c r="F38" t="n">
-        <v>0.04772365960239109</v>
+        <v>0.00725136759035061</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.77%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1800,33 +1806,33 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>FYR</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>회계연도</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.0428885918594519</v>
+        <v>0.03502921300858811</v>
       </c>
       <c r="F39" t="n">
-        <v>0.04288859185945191</v>
+        <v>0.007140166801183734</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.29%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회계연도(FYR). 기여도(정규화 비중)=3.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1836,33 +1842,33 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>gradient_boosting_v1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.03540480263418778</v>
+        <v>0.03132479234126444</v>
       </c>
       <c r="F40" t="n">
-        <v>0.03540480263418778</v>
+        <v>0.006385077571518238</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.54%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.13%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1872,33 +1878,3025 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>gradient_boosting_v1</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MBR_NUM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>회원수</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.02879945093622435</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.00587032553134248</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=2.88%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LAF_CD</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>지방자치단체코드</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.07123498568589968</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.07123498568589968</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DEPT_CD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>부서코드</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.06438996081869364</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.06438996081869364</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.44%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AID_BZR_CAP_CD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>보조사업자시도코드</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.05839048873031386</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.05839048873031386</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>4</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>RPRSV_AGGP_DV_CD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>대표자연령대구분코드</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.05427018714487944</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.05427018714487944</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.43%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>FTEP_STF_NUM</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>상근직원수</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.05358114621860463</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.05358114621860463</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>6</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>RPRSV_HSHD_DV_CD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>대표자세대구분코드</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.05098330684009479</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.05098330684009479</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.10%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>7</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MBR_NUM</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>회원수</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.04893369782155989</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.04893369782155989</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AID_BZR_FNDN_YS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>보조사업자설립년수</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.04303240847945023</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.04303240847945023</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>9</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SECT_CD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>부문코드</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.03644836213775499</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.03644836213775499</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.64%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>10</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>BIZCT_SBAT_AMT</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>사업비보조금금액</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.02993899235451626</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.02993899235451626</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>catboost_v2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AID_BZR_CAP_CD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>보조사업자시도코드</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.08023667168105225</v>
+      </c>
+      <c r="F52" t="n">
+        <v>8.023667168105233</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>catboost_prediction</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=8.02%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>catboost_v2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>INST_TY_CD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>기관유형코드</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.05965870228360584</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5.965870228360589</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>catboost_prediction</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.97%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>3</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>catboost_v2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FTEP_STF_NUM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>상근직원수</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.05335637252486698</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5.335637252486702</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>catboost_prediction</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.34%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>4</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>catboost_v2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DEPT_CD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>부서코드</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.05006322781991538</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5.006322781991543</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>catboost_prediction</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.01%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>5</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>catboost_v2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>RPRSV_AGGP_DV_CD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>대표자연령대구분코드</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.0477082008322463</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4.770820083224634</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>catboost_prediction</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.77%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>6</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>catboost_v2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SECT_CD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>부문코드</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.04639196940201325</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4.639196940201328</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>catboost_prediction</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.64%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>7</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>catboost_v2</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AID_BZR_FNDN_YS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>보조사업자설립년수</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.04564792997314992</v>
+      </c>
+      <c r="F58" t="n">
+        <v>4.564792997314996</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>catboost_prediction</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.56%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>8</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>catboost_v2</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>지자체대비보조사업금액비율</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.03961817449756503</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.961817449756506</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>catboost_prediction</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.96%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>9</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>catboost_v2</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>LAF_CD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>지방자치단체코드</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.03674398613046026</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.674398613046029</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>catboost_prediction</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>10</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>catboost_v2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>RPRSV_HSHD_DV_CD</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>대표자세대구분코드</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.03496440685152415</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3.496440685152419</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>catboost_prediction</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AID_BZR_FNDN_YS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>보조사업자설립년수</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.1523185775533347</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.01038651242041072</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=15.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FTEP_STF_NUM</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>상근직원수</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.1017649070201782</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.006939287956237106</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=10.18%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MBR_NUM</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>회원수</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.09821405086930558</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.006697157205631743</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=9.82%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>지자체수행보조사업수</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.09397932612641352</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.006408393866020934</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=9.40%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>INST_TY_CD</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>기관유형코드</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.06452037139325294</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.004399605416554542</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=6.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>보조금전용신용카드집행건수</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.06323154212367597</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.004311720921890305</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=6.32%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AID_BZR_CAP_CD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>보조사업자시도코드</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.04121623398826991</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.002810510268137334</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.12%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>FYR</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>회계연도</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.03855966753465484</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.00262936059546226</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>변수 의미: 회계연도(FYR). 기여도(정규화 비중)=3.86%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>BIZCT_SUM_AMT</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>사업비합계금액</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.0350877192982458</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.002392610528203665</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>BIZ_MDCN</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>사업개월수</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.02843315184513099</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.001938839565958195</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=2.84%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>FTEP_STF_NUM</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>상근직원수</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.2342891032138918</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.04995247063043684</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.43%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MBR_NUM</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>회원수</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.2169346663918652</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.04625235404896427</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=21.69%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AID_BZR_CAP_CD</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>보조사업자시도코드</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.1177880874367498</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.02511344274056149</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=11.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>LAF_CD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>지방자치단체코드</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.08249876971091312</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.01758945386064037</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=8.25%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>5</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>사업시행지역구분코드</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>0.07900769298714182</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.01684512599766852</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>6</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>THY_PFM_AID_BIZ_NUM</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>당해년도수행보조사업수</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.06972058767860208</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.01486503452605159</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>7</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DEPT_CD</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>부서코드</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.05652179399282405</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.01205093713568295</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>8</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AID_BZR_FNDN_YS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>보조사업자설립년수</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.0448960878910108</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.009572235673930618</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>9</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>RPRSV_HSHD_DV_CD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>대표자세대구분코드</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>0.03046069594404178</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.0064944847995696</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.05%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>10</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BIZCT_SBAT_AMT</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>사업비보조금금액</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>0.02416834560818392</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.005152901085104633</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.42%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>RPRSV_AGGP_DV_CD</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>대표자연령대구분코드</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0.1671891555341897</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.02745224643529737</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=16.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LAF_CD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>지방자치단체코드</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0.1437700029492355</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.02360685140346158</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=14.38%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>3</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AID_BZR_FNDN_YS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>보조사업자설립년수</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0.1015303280210568</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.01667115056945573</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=10.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>DEPT_CD</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>부서코드</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.09202722039563266</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.01511075239888809</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=9.20%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>5</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>FTEP_STF_NUM</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>상근직원수</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0.0667729849588727</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.01096403909963239</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.68%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>6</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AID_BZR_CAP_CD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>보조사업자시도코드</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.06537482659559163</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.01073446327683619</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>7</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MBR_NUM</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>회원수</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.05499786999311703</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.009030580217020967</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>8</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>THY_PFM_AID_BIZ_NUM</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>당해년도수행보조사업수</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0.04788692394236856</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.007862971930768625</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=4.79%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>9</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>지자체대비보조사업금액비율</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0.04465368272728172</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.007332077840552509</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=4.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>10</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BIZ_MDCN</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>사업개월수</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0.04365967951588676</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.007168863779033363</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=4.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>random_forest_v2</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>LAF_CD</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>지방자치단체코드</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0.07254925166059462</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.07254925166059463</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.25%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>DEPT_CD</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>부서코드</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0.0669679439499392</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.06696794394993921</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.70%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AID_BZR_CAP_CD</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>보조사업자시도코드</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0.0584006576381239</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.05840065763812391</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>RPRSV_HSHD_DV_CD</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>대표자세대구분코드</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0.05363503924955487</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.05363503924955488</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>5</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>FTEP_STF_NUM</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>상근직원수</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0.05182978588028408</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.05182978588028409</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.18%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>6</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>RPRSV_AGGP_DV_CD</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>대표자연령대구분코드</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>0.05121974055824543</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.05121974055824544</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>7</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>MBR_NUM</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>회원수</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.04943349195958752</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.04943349195958754</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.94%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>8</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AID_BZR_FNDN_YS</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>보조사업자설립년수</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0.04164635585885659</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.0416463558588566</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.16%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>9</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SECT_CD</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>부문코드</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>0.03624704834575684</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.03624704834575685</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.62%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>10</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BIZCT_SBAT_AMT</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>사업비보조금금액</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>0.03002864339537454</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.03002864339537455</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.00%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>순위(rank)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>알고리즘(algorithm)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>피처명(feature)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>피처명한글(feature_ko)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>기여도비중(importance_share)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>기여도원점수(importance_raw)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>측정방법(method)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>사유(reason)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MBR_NUM</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>회원수</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1027335695024538</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.006969778495202472</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=10.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>INST_TY_CD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>기관유형코드</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.09652091154231966</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.006548291633037551</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=9.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FTEP_STF_NUM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>상근직원수</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.07809443240098939</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.005298179535467795</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BIZ_MDCN</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>사업개월수</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.06968751652302239</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.00472782710070857</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>지자체수행보조사업수</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05950933220535835</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.004037306071204505</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>THY_PFM_AID_BIZ_NUM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>당해년도수행보조사업수</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.05448633215248471</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.003696529459241427</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AID_BZR_CAP_CD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>보조사업자시도코드</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.04909321630624239</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.003330642991660082</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LBST_PLAN_RT</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>인건비계획비율</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.04446676888912223</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.003016769796430951</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=4.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BIZCT_PYHWY_AMT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>사업비자부담금액</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.03666790038597665</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.002487669267330406</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>보조금전용신용카드집행건수</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0365357161740591</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.002478701461752442</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=3.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>순위(rank)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>알고리즘(algorithm)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>피처명(feature)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>피처명한글(feature_ko)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>기여도비중(importance_share)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>기여도원점수(importance_raw)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>측정방법(method)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>사유(reason)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AID_BZR_FNDN_YS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>보조사업자설립년수</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1523185775533347</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.01038651242041072</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=15.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FTEP_STF_NUM</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>상근직원수</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1017649070201782</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.006939287956237106</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=10.18%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>MBR_NUM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>회원수</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.09821405086930558</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.006697157205631743</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=9.82%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>지자체수행보조사업수</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.09397932612641352</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.006408393866020934</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=9.40%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>INST_TY_CD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>기관유형코드</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06452037139325294</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.004399605416554542</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=6.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>보조금전용신용카드집행건수</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.06323154212367597</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.004311720921890305</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=6.32%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AID_BZR_CAP_CD</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>보조사업자시도코드</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.04121623398826991</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.002810510268137334</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.12%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FYR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>회계연도</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03855966753465484</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.00262936059546226</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>변수 의미: 회계연도(FYR). 기여도(정규화 비중)=3.86%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>사업비합계금액</t>
         </is>
       </c>
-      <c r="E41" t="n">
-        <v>0.02928295777591394</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.02928295777591394</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>tree_impurity</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.93%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+      <c r="E10" t="n">
+        <v>0.0350877192982458</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.002392610528203665</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>stacked_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BIZ_MDCN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>사업개월수</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.02843315184513099</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.001938839565958195</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=2.84%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1969,19 +4967,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.06512370292287779</v>
+        <v>0.06671461789117154</v>
       </c>
       <c r="F2" t="n">
-        <v>6.512370292287774</v>
+        <v>6.671461789117155</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -1990,7 +4988,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.51%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2005,19 +5003,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06218461134590617</v>
+        <v>0.06495441989195058</v>
       </c>
       <c r="F3" t="n">
-        <v>6.218461134590611</v>
+        <v>6.495441989195059</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2026,7 +5024,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.22%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2041,19 +5039,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0586404025870892</v>
+        <v>0.05547755973096497</v>
       </c>
       <c r="F4" t="n">
-        <v>5.864040258708916</v>
+        <v>5.547755973096498</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2062,7 +5060,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.86%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.55%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2077,19 +5075,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.04820782632383652</v>
+        <v>0.05417814811546744</v>
       </c>
       <c r="F5" t="n">
-        <v>4.820782632383648</v>
+        <v>5.417814811546745</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2098,7 +5096,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.82%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2113,19 +5111,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04747477439020054</v>
+        <v>0.05058522443296955</v>
       </c>
       <c r="F6" t="n">
-        <v>4.74747743902005</v>
+        <v>5.058522443296956</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2134,7 +5132,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.75%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2149,19 +5147,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04480735044966697</v>
+        <v>0.04458071949171321</v>
       </c>
       <c r="F7" t="n">
-        <v>4.480735044966694</v>
+        <v>4.458071949171321</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2170,7 +5168,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.46%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2185,19 +5183,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04033593740657232</v>
+        <v>0.04060187085898578</v>
       </c>
       <c r="F8" t="n">
-        <v>4.033593740657229</v>
+        <v>4.060187085898579</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2206,7 +5204,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.03%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2221,19 +5219,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03634252123369216</v>
+        <v>0.03611816776722611</v>
       </c>
       <c r="F9" t="n">
-        <v>3.634252123369213</v>
+        <v>3.611816776722611</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2242,7 +5240,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.63%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2257,19 +5255,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03377831181233264</v>
+        <v>0.03477271178468273</v>
       </c>
       <c r="F10" t="n">
-        <v>3.377831181233262</v>
+        <v>3.477271178468274</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2278,7 +5276,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=3.38%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2293,19 +5291,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03369229173308515</v>
+        <v>0.0344039068366</v>
       </c>
       <c r="F11" t="n">
-        <v>3.369229173308512</v>
+        <v>3.44039068366</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2314,7 +5312,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.37%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.44%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2394,10 +5392,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07850951358445041</v>
+        <v>0.08023667168105225</v>
       </c>
       <c r="F2" t="n">
-        <v>7.850951358445034</v>
+        <v>8.023667168105233</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2406,7 +5404,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.85%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=8.02%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2421,19 +5419,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.05953418487611781</v>
+        <v>0.05965870228360584</v>
       </c>
       <c r="F3" t="n">
-        <v>5.953418487611776</v>
+        <v>5.965870228360589</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2442,7 +5440,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.95%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.97%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2457,19 +5455,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05902799501884216</v>
+        <v>0.05335637252486698</v>
       </c>
       <c r="F4" t="n">
-        <v>5.902799501884211</v>
+        <v>5.335637252486702</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2478,7 +5476,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.90%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.34%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2493,19 +5491,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05060763118691404</v>
+        <v>0.05006322781991538</v>
       </c>
       <c r="F5" t="n">
-        <v>5.060763118691399</v>
+        <v>5.006322781991543</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2514,7 +5512,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.01%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2529,19 +5527,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04418441392537081</v>
+        <v>0.0477082008322463</v>
       </c>
       <c r="F6" t="n">
-        <v>4.418441392537077</v>
+        <v>4.770820083224634</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2550,7 +5548,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.77%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2565,19 +5563,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04395703343026858</v>
+        <v>0.04639196940201325</v>
       </c>
       <c r="F7" t="n">
-        <v>4.395703343026854</v>
+        <v>4.639196940201328</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -2586,7 +5584,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.40%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.64%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2601,19 +5599,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04225371024686373</v>
+        <v>0.04564792997314992</v>
       </c>
       <c r="F8" t="n">
-        <v>4.225371024686369</v>
+        <v>4.564792997314996</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2622,7 +5620,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.23%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.56%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2646,10 +5644,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03613249857830451</v>
+        <v>0.03961817449756503</v>
       </c>
       <c r="F9" t="n">
-        <v>3.613249857830448</v>
+        <v>3.961817449756506</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2658,7 +5656,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.96%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2673,19 +5671,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03327229716580977</v>
+        <v>0.03674398613046026</v>
       </c>
       <c r="F10" t="n">
-        <v>3.327229716580975</v>
+        <v>3.674398613046029</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2694,7 +5692,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.33%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2709,19 +5707,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03315060255846319</v>
+        <v>0.03496440685152415</v>
       </c>
       <c r="F11" t="n">
-        <v>3.315060255846316</v>
+        <v>3.496440685152419</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2730,7 +5728,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.32%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2796,33 +5794,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07128537539281089</v>
+        <v>0.2369881283651408</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07128537539281089</v>
+        <v>0.05162945027351795</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.13%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2832,33 +5830,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06794269690533204</v>
+        <v>0.212956712166369</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06794269690533204</v>
+        <v>0.04639404537709613</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.79%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=21.30%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2868,7 +5866,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2882,19 +5880,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.06032811954240906</v>
+        <v>0.1194243656661127</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06032811954240906</v>
+        <v>0.02601739754282112</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.03%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=11.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2904,33 +5902,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05352744284457885</v>
+        <v>0.0909143299359494</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05352744284457885</v>
+        <v>0.01980629539951562</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2940,33 +5938,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05347886914881447</v>
+        <v>0.07733439810317347</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05347886914881447</v>
+        <v>0.01684781633934174</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.73%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2976,33 +5974,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05220979045101741</v>
+        <v>0.05831261422949655</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05220979045101741</v>
+        <v>0.01270379338175942</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.22%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3012,33 +6010,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04822499703852008</v>
+        <v>0.04704197059259392</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04822499703852008</v>
+        <v>0.01024840821450984</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.82%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3048,7 +6046,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3062,19 +6060,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04229378740443412</v>
+        <v>0.04169891162959222</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04229378740443412</v>
+        <v>0.009084387050488751</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.17%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3084,33 +6082,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03490214011419904</v>
+        <v>0.03488218925460607</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03490214011419904</v>
+        <v>0.007599318446775971</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.49%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3120,33 +6118,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>random_forest_v1</t>
+          <t>easy_ensemble_v1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02968403128616421</v>
+        <v>0.03102925921657064</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02968403128616421</v>
+        <v>0.006759931844677491</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.97%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3212,33 +6210,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>easy_ensemble_v2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07143149908118701</v>
+        <v>0.2342891032138918</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07143149908118702</v>
+        <v>0.04995247063043684</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.14%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.43%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3248,33 +6246,33 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>easy_ensemble_v2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0658730897024364</v>
+        <v>0.2169346663918652</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06587308970243641</v>
+        <v>0.04625235404896427</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.59%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=21.69%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3284,7 +6282,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>easy_ensemble_v2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3298,19 +6296,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.06240819698226026</v>
+        <v>0.1177880874367498</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06240819698226027</v>
+        <v>0.02511344274056149</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.24%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=11.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3320,33 +6318,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>easy_ensemble_v2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05227164345278072</v>
+        <v>0.08249876971091312</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05227164345278074</v>
+        <v>0.01758945386064037</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=8.25%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3356,33 +6354,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>easy_ensemble_v2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05156726898647793</v>
+        <v>0.07900769298714182</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05156726898647795</v>
+        <v>0.01684512599766852</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.16%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3392,33 +6390,33 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>easy_ensemble_v2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04990558558890892</v>
+        <v>0.06972058767860208</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04990558558890893</v>
+        <v>0.01486503452605159</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3428,33 +6426,33 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>easy_ensemble_v2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04772365960239108</v>
+        <v>0.05652179399282405</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04772365960239109</v>
+        <v>0.01205093713568295</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.77%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3464,7 +6462,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>easy_ensemble_v2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3478,19 +6476,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0428885918594519</v>
+        <v>0.0448960878910108</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04288859185945191</v>
+        <v>0.009572235673930618</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.29%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3500,33 +6498,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>random_forest_v2</t>
+          <t>easy_ensemble_v2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03540480263418778</v>
+        <v>0.03046069594404178</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03540480263418778</v>
+        <v>0.0064944847995696</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tree_impurity</t>
+          <t>permutation_roc_auc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.54%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.05%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3536,24 +6534,1688 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>easy_ensemble_v2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BIZCT_SBAT_AMT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>사업비보조금금액</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.02416834560818392</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.005152901085104633</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.42%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>순위(rank)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>알고리즘(algorithm)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>피처명(feature)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>피처명한글(feature_ko)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>기여도비중(importance_share)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>기여도원점수(importance_raw)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>측정방법(method)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>사유(reason)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RPRSV_AGGP_DV_CD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>대표자연령대구분코드</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2662079403069144</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.05426239799121152</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=26.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AID_BZR_FNDN_YS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>보조사업자설립년수</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1355325214698025</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02762622186350999</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=13.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LAF_CD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>지방자치단체코드</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1189286217091377</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.02424177203838218</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=11.89%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FTEP_STF_NUM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>상근직원수</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.06474377023792785</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01319702268854805</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AID_BZR_CAP_CD</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>보조사업자시도코드</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05747571448683674</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01171554120706658</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>DEPT_CD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>부서코드</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.04826305786287505</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.009837682719038621</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>지자체대비보조사업금액비율</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.03557475714486848</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.00725136759035061</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FYR</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>회계연도</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03502921300858811</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.007140166801183734</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>변수 의미: 회계연도(FYR). 기여도(정규화 비중)=3.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>THY_PFM_AID_BIZ_NUM</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>당해년도수행보조사업수</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.03132479234126444</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.006385077571518238</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.13%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MBR_NUM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>회원수</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.02879945093622435</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.00587032553134248</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=2.88%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>순위(rank)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>알고리즘(algorithm)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>피처명(feature)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>피처명한글(feature_ko)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>기여도비중(importance_share)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>기여도원점수(importance_raw)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>측정방법(method)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>사유(reason)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RPRSV_AGGP_DV_CD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>대표자연령대구분코드</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.1671891555341897</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.02745224643529737</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=16.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LAF_CD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>지방자치단체코드</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1437700029492355</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.02360685140346158</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=14.38%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AID_BZR_FNDN_YS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>보조사업자설립년수</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1015303280210568</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.01667115056945573</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=10.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DEPT_CD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>부서코드</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.09202722039563266</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.01511075239888809</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=9.20%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FTEP_STF_NUM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>상근직원수</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0667729849588727</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01096403909963239</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.68%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AID_BZR_CAP_CD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>보조사업자시도코드</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.06537482659559163</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.01073446327683619</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MBR_NUM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>회원수</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.05499786999311703</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.009030580217020967</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>THY_PFM_AID_BIZ_NUM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>당해년도수행보조사업수</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.04788692394236856</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.007862971930768625</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=4.79%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>지자체대비보조사업금액비율</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.04465368272728172</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.007332077840552509</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=4.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>gradient_boosting_v2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BIZ_MDCN</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>사업개월수</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.04365967951588676</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.007168863779033363</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>permutation_roc_auc</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=4.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>순위(rank)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>알고리즘(algorithm)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>피처명(feature)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>피처명한글(feature_ko)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>기여도비중(importance_share)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>기여도원점수(importance_raw)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>측정방법(method)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>사유(reason)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LAF_CD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>지방자치단체코드</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.07123498568589968</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07123498568589968</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DEPT_CD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>부서코드</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.06438996081869364</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.06438996081869364</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.44%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AID_BZR_CAP_CD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>보조사업자시도코드</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.05839048873031386</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05839048873031386</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RPRSV_AGGP_DV_CD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>대표자연령대구분코드</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05427018714487944</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.05427018714487944</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.43%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FTEP_STF_NUM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>상근직원수</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05358114621860463</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.05358114621860463</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RPRSV_HSHD_DV_CD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>대표자세대구분코드</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.05098330684009479</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05098330684009479</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.10%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MBR_NUM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>회원수</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.04893369782155989</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04893369782155989</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AID_BZR_FNDN_YS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>보조사업자설립년수</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.04303240847945023</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.04303240847945023</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SECT_CD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>부문코드</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.03644836213775499</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.03644836213775499</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.64%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>random_forest_v1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BIZCT_SBAT_AMT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>사업비보조금금액</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.02993899235451626</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.02993899235451626</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>순위(rank)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>알고리즘(algorithm)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>피처명(feature)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>피처명한글(feature_ko)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>기여도비중(importance_share)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>기여도원점수(importance_raw)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>측정방법(method)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>사유(reason)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>random_forest_v2</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LAF_CD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>지방자치단체코드</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.07254925166059462</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.07254925166059463</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.25%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DEPT_CD</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>부서코드</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.0669679439499392</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.06696794394993921</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.70%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AID_BZR_CAP_CD</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>보조사업자시도코드</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0584006576381239</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05840065763812391</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>RPRSV_HSHD_DV_CD</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>대표자세대구분코드</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05363503924955487</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.05363503924955488</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FTEP_STF_NUM</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>상근직원수</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05182978588028408</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.05182978588028409</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.18%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>RPRSV_AGGP_DV_CD</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>대표자연령대구분코드</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.05121974055824543</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05121974055824544</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>MBR_NUM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>회원수</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.04943349195958752</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.04943349195958754</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.94%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AID_BZR_FNDN_YS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>보조사업자설립년수</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.04164635585885659</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0416463558588566</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.16%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SECT_CD</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>부문코드</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.03624704834575684</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.03624704834575685</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tree_impurity</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.62%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>random_forest_v2</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02928295777591394</v>
+        <v>0.03002864339537454</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02928295777591394</v>
+        <v>0.03002864339537455</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -3562,7 +8224,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=2.93%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.00%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>

--- a/outputs/reports/comparison/feature_importance_top10_all.xlsx
+++ b/outputs/reports/comparison/feature_importance_top10_all.xlsx
@@ -479,19 +479,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.06671461789117154</v>
+        <v>0.06762103693331124</v>
       </c>
       <c r="F2" t="n">
-        <v>6.671461789117155</v>
+        <v>6.762103693331121</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -500,7 +500,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.76%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -515,19 +515,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06495441989195058</v>
+        <v>0.06558865971786301</v>
       </c>
       <c r="F3" t="n">
-        <v>6.495441989195059</v>
+        <v>6.558865971786298</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -536,7 +536,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.56%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -551,19 +551,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05547755973096497</v>
+        <v>0.05638176459826573</v>
       </c>
       <c r="F4" t="n">
-        <v>5.547755973096498</v>
+        <v>5.63817645982657</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.55%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.64%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -587,19 +587,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05417814811546744</v>
+        <v>0.04176772834277437</v>
       </c>
       <c r="F5" t="n">
-        <v>5.417814811546745</v>
+        <v>4.176772834277435</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.18%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -623,19 +623,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05058522443296955</v>
+        <v>0.04140493817864251</v>
       </c>
       <c r="F6" t="n">
-        <v>5.058522443296956</v>
+        <v>4.140493817864249</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.14%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -659,19 +659,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04458071949171321</v>
+        <v>0.03586576551426982</v>
       </c>
       <c r="F7" t="n">
-        <v>4.458071949171321</v>
+        <v>3.58657655142698</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.46%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=3.59%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -695,19 +695,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04060187085898578</v>
+        <v>0.03486040528587571</v>
       </c>
       <c r="F8" t="n">
-        <v>4.060187085898579</v>
+        <v>3.486040528587569</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=3.49%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -731,19 +731,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03611816776722611</v>
+        <v>0.03306797514035693</v>
       </c>
       <c r="F9" t="n">
-        <v>3.611816776722611</v>
+        <v>3.306797514035692</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.31%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -767,19 +767,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>FLD_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>분야코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03477271178468273</v>
+        <v>0.03270175100360688</v>
       </c>
       <c r="F10" t="n">
-        <v>3.477271178468274</v>
+        <v>3.270175100360686</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 분야코드(FLD_CD). 기여도(정규화 비중)=3.27%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -803,19 +803,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>지자체수행보조사업수</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0344039068366</v>
+        <v>0.02953478423868656</v>
       </c>
       <c r="F11" t="n">
-        <v>3.44039068366</v>
+        <v>2.953478423868654</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.44%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=2.95%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -839,19 +839,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.1027335695024538</v>
+        <v>0.2335976928622889</v>
       </c>
       <c r="F12" t="n">
-        <v>0.006969778495202472</v>
+        <v>0.05302921809376565</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=10.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.36%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -875,19 +875,19 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09652091154231966</v>
+        <v>0.2134295499021494</v>
       </c>
       <c r="F13" t="n">
-        <v>0.006548291633037551</v>
+        <v>0.0484508301890102</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=9.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=21.34%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -911,19 +911,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.07809443240098939</v>
+        <v>0.1053661551138105</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005298179535467795</v>
+        <v>0.02391926371689701</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=10.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -947,19 +947,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.06968751652302239</v>
+        <v>0.08503064167267367</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00472782710070857</v>
+        <v>0.01930288089177007</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=8.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -983,19 +983,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>지자체수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.05950933220535835</v>
+        <v>0.04363863425687455</v>
       </c>
       <c r="F16" t="n">
-        <v>0.004037306071204505</v>
+        <v>0.009906444815300897</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=4.36%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1019,19 +1019,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.05448633215248471</v>
+        <v>0.03056442476053147</v>
       </c>
       <c r="F17" t="n">
-        <v>0.003696529459241427</v>
+        <v>0.006938456997056974</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=3.06%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1055,19 +1055,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.04909321630624239</v>
+        <v>0.02850448037902963</v>
       </c>
       <c r="F18" t="n">
-        <v>0.003330642991660082</v>
+        <v>0.006470827207870289</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=2.85%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1091,19 +1091,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.04446676888912223</v>
+        <v>0.02491888968997853</v>
       </c>
       <c r="F19" t="n">
-        <v>0.003016769796430951</v>
+        <v>0.005656859106067336</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=4.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=2.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1127,19 +1127,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.03666790038597665</v>
+        <v>0.02480945514471095</v>
       </c>
       <c r="F20" t="n">
-        <v>0.002487669267330406</v>
+        <v>0.005632016273516727</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=2.48%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1163,19 +1163,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>보조금전용신용카드집행건수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.0365357161740591</v>
+        <v>0.02475151920898096</v>
       </c>
       <c r="F21" t="n">
-        <v>0.002478701461752442</v>
+        <v>0.005618864185695793</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=3.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=2.48%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1199,19 +1199,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.2369881283651408</v>
+        <v>0.2936518688692807</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05162945027351795</v>
+        <v>0.07443643303687553</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=29.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1235,19 +1235,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.212956712166369</v>
+        <v>0.2751346848417932</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04639404537709613</v>
+        <v>0.06974259902791458</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=21.30%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=27.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1271,19 +1271,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.1194243656661127</v>
+        <v>0.07662839666667617</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02601739754282112</v>
+        <v>0.01942417236834032</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=11.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=7.66%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1307,19 +1307,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.0909143299359494</v>
+        <v>0.06540393922535705</v>
       </c>
       <c r="F25" t="n">
-        <v>0.01980629539951562</v>
+        <v>0.01657893736975791</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1343,19 +1343,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.07733439810317347</v>
+        <v>0.06234848856079634</v>
       </c>
       <c r="F26" t="n">
-        <v>0.01684781633934174</v>
+        <v>0.01580442553141748</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.73%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=6.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1379,19 +1379,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.05831261422949655</v>
+        <v>0.05386240671507315</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01270379338175942</v>
+        <v>0.0136533285011588</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=5.39%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1415,19 +1415,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.04704197059259392</v>
+        <v>0.02828309615157349</v>
       </c>
       <c r="F28" t="n">
-        <v>0.01024840821450984</v>
+        <v>0.007169349205467801</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=2.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1451,19 +1451,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>CUMU_PYHWY_EXE_AMT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>누적자부담집행금액</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.04169891162959222</v>
+        <v>0.02717621591082704</v>
       </c>
       <c r="F29" t="n">
-        <v>0.009084387050488751</v>
+        <v>0.006888771331955812</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.17%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 누적자부담집행금액(CUMU_PYHWY_EXE_AMT). 기여도(정규화 비중)=2.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1487,19 +1487,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.03488218925460607</v>
+        <v>0.02492786542181072</v>
       </c>
       <c r="F30" t="n">
-        <v>0.007599318446775971</v>
+        <v>0.006318847526384563</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=2.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1523,19 +1523,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.03102925921657064</v>
+        <v>0.01588834345571474</v>
       </c>
       <c r="F31" t="n">
-        <v>0.006759931844677491</v>
+        <v>0.004027461559370005</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=1.59%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1559,19 +1559,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.2662079403069144</v>
+        <v>0.1947102492449268</v>
       </c>
       <c r="F32" t="n">
-        <v>0.05426239799121152</v>
+        <v>0.06048206785892779</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=26.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=19.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1595,19 +1595,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.1355325214698025</v>
+        <v>0.1458445065439734</v>
       </c>
       <c r="F33" t="n">
-        <v>0.02762622186350999</v>
+        <v>0.04530309717054748</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=13.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=14.58%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1631,19 +1631,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.1189286217091377</v>
+        <v>0.1120755356084346</v>
       </c>
       <c r="F34" t="n">
-        <v>0.02424177203838218</v>
+        <v>0.03481357646185457</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=11.89%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=11.21%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1667,19 +1667,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.06474377023792785</v>
+        <v>0.1041060961037252</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01319702268854805</v>
+        <v>0.03233806126534772</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=10.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.05747571448683674</v>
+        <v>0.07371025865394595</v>
       </c>
       <c r="F36" t="n">
-        <v>0.01171554120706658</v>
+        <v>0.02289632355305116</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1739,19 +1739,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.04826305786287505</v>
+        <v>0.04473047863682122</v>
       </c>
       <c r="F37" t="n">
-        <v>0.009837682719038621</v>
+        <v>0.01389445011120816</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1775,19 +1775,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>CARD_FR_USE_CNT</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>지자체대비보조사업금액비율</t>
+          <t>카드해외사용건수</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.03557475714486848</v>
+        <v>0.04181838710588008</v>
       </c>
       <c r="F38" t="n">
-        <v>0.00725136759035061</v>
+        <v>0.01298987873775037</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 카드해외사용건수(CARD_FR_USE_CNT). 기여도(정규화 비중)=4.18%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1811,19 +1811,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FYR</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>회계연도</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.03502921300858811</v>
+        <v>0.03752316971048448</v>
       </c>
       <c r="F39" t="n">
-        <v>0.007140166801183734</v>
+        <v>0.01165567249547711</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>변수 의미: 회계연도(FYR). 기여도(정규화 비중)=3.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=3.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1847,19 +1847,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.03132479234126444</v>
+        <v>0.02720617984399845</v>
       </c>
       <c r="F40" t="n">
-        <v>0.006385077571518238</v>
+        <v>0.008450947096457384</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.13%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=2.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1883,19 +1883,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.02879945093622435</v>
+        <v>0.02115147580470616</v>
       </c>
       <c r="F41" t="n">
-        <v>0.00587032553134248</v>
+        <v>0.00657019853807228</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=2.88%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=2.12%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -1919,19 +1919,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.07123498568589968</v>
+        <v>0.07861920191648994</v>
       </c>
       <c r="F42" t="n">
-        <v>0.07123498568589968</v>
+        <v>0.07861920191648994</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.86%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1955,19 +1955,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.06438996081869364</v>
+        <v>0.0532840740558066</v>
       </c>
       <c r="F43" t="n">
-        <v>0.06438996081869364</v>
+        <v>0.0532840740558066</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.44%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.33%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -1991,19 +1991,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.05839048873031386</v>
+        <v>0.053014598924571</v>
       </c>
       <c r="F44" t="n">
-        <v>0.05839048873031386</v>
+        <v>0.053014598924571</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=5.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2027,19 +2027,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.05427018714487944</v>
+        <v>0.05061020905280734</v>
       </c>
       <c r="F45" t="n">
-        <v>0.05427018714487944</v>
+        <v>0.05061020905280734</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.43%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=5.06%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2063,19 +2063,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.05358114621860463</v>
+        <v>0.04959939767759144</v>
       </c>
       <c r="F46" t="n">
-        <v>0.05358114621860463</v>
+        <v>0.04959939767759144</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.96%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2099,19 +2099,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.05098330684009479</v>
+        <v>0.03354108819730399</v>
       </c>
       <c r="F47" t="n">
-        <v>0.05098330684009479</v>
+        <v>0.03354108819730399</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.10%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2135,19 +2135,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.04893369782155989</v>
+        <v>0.03143857980808221</v>
       </c>
       <c r="F48" t="n">
-        <v>0.04893369782155989</v>
+        <v>0.03143857980808221</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.14%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2171,19 +2171,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.04303240847945023</v>
+        <v>0.03080299006641432</v>
       </c>
       <c r="F49" t="n">
-        <v>0.04303240847945023</v>
+        <v>0.03080299006641432</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.08%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2207,19 +2207,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.03644836213775499</v>
+        <v>0.02956599781773235</v>
       </c>
       <c r="F50" t="n">
-        <v>0.03644836213775499</v>
+        <v>0.02956599781773235</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.64%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.96%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2243,19 +2243,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.02993899235451626</v>
+        <v>0.02851796918745795</v>
       </c>
       <c r="F51" t="n">
-        <v>0.02993899235451626</v>
+        <v>0.02851796918745795</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=2.85%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.08023667168105225</v>
+        <v>0.07427712080084094</v>
       </c>
       <c r="F52" t="n">
-        <v>8.023667168105233</v>
+        <v>7.427712080084095</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=8.02%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.43%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2315,19 +2315,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.05965870228360584</v>
+        <v>0.06172011341010498</v>
       </c>
       <c r="F53" t="n">
-        <v>5.965870228360589</v>
+        <v>6.172011341010498</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.97%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.17%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.05335637252486698</v>
+        <v>0.05379237014250506</v>
       </c>
       <c r="F54" t="n">
-        <v>5.335637252486702</v>
+        <v>5.379237014250506</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.34%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.38%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2387,19 +2387,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.05006322781991538</v>
+        <v>0.04966963952217231</v>
       </c>
       <c r="F55" t="n">
-        <v>5.006322781991543</v>
+        <v>4.966963952217232</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.01%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.97%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2423,19 +2423,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0477082008322463</v>
+        <v>0.04847747741277377</v>
       </c>
       <c r="F56" t="n">
-        <v>4.770820083224634</v>
+        <v>4.847747741277378</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.77%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=4.85%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2459,19 +2459,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.04639196940201325</v>
+        <v>0.04379704642749314</v>
       </c>
       <c r="F57" t="n">
-        <v>4.639196940201328</v>
+        <v>4.379704642749314</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.64%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.38%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2495,19 +2495,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>FLD_CD</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>분야코드</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.04564792997314992</v>
+        <v>0.04286335922902603</v>
       </c>
       <c r="F58" t="n">
-        <v>4.564792997314996</v>
+        <v>4.286335922902603</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.56%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 분야코드(FLD_CD). 기여도(정규화 비중)=4.29%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.03961817449756503</v>
+        <v>0.0357887121699075</v>
       </c>
       <c r="F59" t="n">
-        <v>3.961817449756506</v>
+        <v>3.57887121699075</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.96%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.58%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2567,19 +2567,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.03674398613046026</v>
+        <v>0.03530508698139623</v>
       </c>
       <c r="F60" t="n">
-        <v>3.674398613046029</v>
+        <v>3.530508698139623</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.53%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2603,19 +2603,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.03496440685152415</v>
+        <v>0.03030561248217348</v>
       </c>
       <c r="F61" t="n">
-        <v>3.496440685152419</v>
+        <v>3.030561248217349</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=3.03%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -2639,19 +2639,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.1523185775533347</v>
+        <v>0.1720786854411036</v>
       </c>
       <c r="F62" t="n">
-        <v>0.01038651242041072</v>
+        <v>0.0481293347089442</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=15.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=17.21%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2675,19 +2675,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.1017649070201782</v>
+        <v>0.09087489223856447</v>
       </c>
       <c r="F63" t="n">
-        <v>0.006939287956237106</v>
+        <v>0.02541714038538539</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=10.18%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=9.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2711,19 +2711,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.09821405086930558</v>
+        <v>0.08293320097181266</v>
       </c>
       <c r="F64" t="n">
-        <v>0.006697157205631743</v>
+        <v>0.02319589888674889</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=9.82%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=8.29%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2747,19 +2747,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>지자체수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.09397932612641352</v>
+        <v>0.05972465320410667</v>
       </c>
       <c r="F65" t="n">
-        <v>0.006408393866020934</v>
+        <v>0.01670461287560165</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=9.40%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=5.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2783,19 +2783,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.06452037139325294</v>
+        <v>0.05431698842707499</v>
       </c>
       <c r="F66" t="n">
-        <v>0.004399605416554542</v>
+        <v>0.01519212277620113</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=6.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=5.43%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>보조금전용신용카드집행건수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.06323154212367597</v>
+        <v>0.05205987617231388</v>
       </c>
       <c r="F67" t="n">
-        <v>0.004311720921890305</v>
+        <v>0.01456082256079916</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=6.32%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.21%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2855,19 +2855,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>CORP_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>법인사업자누적집행건수</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.04121623398826991</v>
+        <v>0.04831892160192288</v>
       </c>
       <c r="F68" t="n">
-        <v>0.002810510268137334</v>
+        <v>0.01351450090749406</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.12%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 법인사업자누적집행건수(CORP_BZR_CUMU_EXE_CNT). 기여도(정규화 비중)=4.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FYR</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>회계연도</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.03855966753465484</v>
+        <v>0.04407116173358786</v>
       </c>
       <c r="F69" t="n">
-        <v>0.00262936059546226</v>
+        <v>0.01232642897434177</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>변수 의미: 회계연도(FYR). 기여도(정규화 비중)=3.86%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2927,19 +2927,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.0350877192982458</v>
+        <v>0.04359570521695944</v>
       </c>
       <c r="F70" t="n">
-        <v>0.002392610528203665</v>
+        <v>0.01219344675304168</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=4.36%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2963,19 +2963,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>LBST_EXE_AVG_AMT</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>인건비집행평균금액</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.02843315184513099</v>
+        <v>0.03278037566289588</v>
       </c>
       <c r="F71" t="n">
-        <v>0.001938839565958195</v>
+        <v>0.009168466554240584</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=2.84%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비집행평균금액(LBST_EXE_AVG_AMT). 기여도(정규화 비중)=3.28%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -2999,19 +2999,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.2342891032138918</v>
+        <v>0.2862142282496265</v>
       </c>
       <c r="F72" t="n">
-        <v>0.04995247063043684</v>
+        <v>0.07278511534381027</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.43%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=28.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3035,19 +3035,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.2169346663918652</v>
+        <v>0.2770658544994826</v>
       </c>
       <c r="F73" t="n">
-        <v>0.04625235404896427</v>
+        <v>0.07045865714260663</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=21.69%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=27.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3071,19 +3071,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.1177880874367498</v>
+        <v>0.07052062981266526</v>
       </c>
       <c r="F74" t="n">
-        <v>0.02511344274056149</v>
+        <v>0.01793360241530789</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=11.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=7.05%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3107,19 +3107,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.08249876971091312</v>
+        <v>0.06964142052637631</v>
       </c>
       <c r="F75" t="n">
-        <v>0.01758945386064037</v>
+        <v>0.01771001692235302</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=8.25%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.96%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.07900769298714182</v>
+        <v>0.06402712331915868</v>
       </c>
       <c r="F76" t="n">
-        <v>0.01684512599766852</v>
+        <v>0.01628228472224252</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=6.40%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3179,19 +3179,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.06972058767860208</v>
+        <v>0.04801746925640723</v>
       </c>
       <c r="F77" t="n">
-        <v>0.01486503452605159</v>
+        <v>0.01221098287013628</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=4.80%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3215,19 +3215,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>CUMU_PYHWY_EXE_AMT</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>누적자부담집행금액</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.05652179399282405</v>
+        <v>0.03201930812550288</v>
       </c>
       <c r="F78" t="n">
-        <v>0.01205093713568295</v>
+        <v>0.008142603704212492</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 누적자부담집행금액(CUMU_PYHWY_EXE_AMT). 기여도(정규화 비중)=3.20%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3251,19 +3251,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.0448960878910108</v>
+        <v>0.02490518331226298</v>
       </c>
       <c r="F79" t="n">
-        <v>0.009572235673930618</v>
+        <v>0.006333460957296644</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=2.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3287,19 +3287,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.03046069594404178</v>
+        <v>0.02120445925755662</v>
       </c>
       <c r="F80" t="n">
-        <v>0.0064944847995696</v>
+        <v>0.005392356006558519</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.05%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=2.12%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3323,19 +3323,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.02416834560818392</v>
+        <v>0.01723939777037119</v>
       </c>
       <c r="F81" t="n">
-        <v>0.005152901085104633</v>
+        <v>0.004384029273624801</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.42%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=1.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3359,19 +3359,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.1671891555341897</v>
+        <v>0.2374525038280519</v>
       </c>
       <c r="F82" t="n">
-        <v>0.02745224643529737</v>
+        <v>0.05506779170600101</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=16.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3395,19 +3395,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.1437700029492355</v>
+        <v>0.1477847722389224</v>
       </c>
       <c r="F83" t="n">
-        <v>0.02360685140346158</v>
+        <v>0.03427287951810748</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=14.38%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=14.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3431,19 +3431,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.1015303280210568</v>
+        <v>0.1318739484678361</v>
       </c>
       <c r="F84" t="n">
-        <v>0.01667115056945573</v>
+        <v>0.03058298821280653</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=10.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=13.19%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3467,19 +3467,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.09202722039563266</v>
+        <v>0.08831294857495794</v>
       </c>
       <c r="F85" t="n">
-        <v>0.01511075239888809</v>
+        <v>0.02048072342328378</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=9.20%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=8.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3503,19 +3503,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.0667729849588727</v>
+        <v>0.04938341619564358</v>
       </c>
       <c r="F86" t="n">
-        <v>0.01096403909963239</v>
+        <v>0.01145254580579913</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.68%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.06537482659559163</v>
+        <v>0.04835000031506613</v>
       </c>
       <c r="F87" t="n">
-        <v>0.01073446327683619</v>
+        <v>0.01121288553884098</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.84%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3575,19 +3575,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>NTS_BT_CD</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>국세청업종코드</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.05499786999311703</v>
+        <v>0.03432327013113043</v>
       </c>
       <c r="F88" t="n">
-        <v>0.009030580217020967</v>
+        <v>0.007959935817811348</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 국세청업종코드(NTS_BT_CD). 기여도(정규화 비중)=3.43%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3611,19 +3611,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.04788692394236856</v>
+        <v>0.03111590011153352</v>
       </c>
       <c r="F89" t="n">
-        <v>0.007862971930768625</v>
+        <v>0.007216112184386392</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=4.79%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=3.11%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3647,19 +3647,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>지자체대비보조사업금액비율</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.04465368272728172</v>
+        <v>0.02727839845743778</v>
       </c>
       <c r="F90" t="n">
-        <v>0.007332077840552509</v>
+        <v>0.00632615424184052</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=4.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=2.73%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3683,19 +3683,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.04365967951588676</v>
+        <v>0.02534389433952774</v>
       </c>
       <c r="F91" t="n">
-        <v>0.007168863779033363</v>
+        <v>0.005877521912839634</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=4.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=2.53%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -3719,19 +3719,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.07254925166059462</v>
+        <v>0.07577859416271837</v>
       </c>
       <c r="F92" t="n">
-        <v>0.07254925166059463</v>
+        <v>0.07577859416271837</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.25%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.58%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3755,19 +3755,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.0669679439499392</v>
+        <v>0.0534527252886216</v>
       </c>
       <c r="F93" t="n">
-        <v>0.06696794394993921</v>
+        <v>0.0534527252886216</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.70%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.0584006576381239</v>
+        <v>0.05111454479859059</v>
       </c>
       <c r="F94" t="n">
-        <v>0.05840065763812391</v>
+        <v>0.05111454479859059</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.11%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3827,19 +3827,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.05363503924955487</v>
+        <v>0.04893739718600483</v>
       </c>
       <c r="F95" t="n">
-        <v>0.05363503924955488</v>
+        <v>0.04893739718600483</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3863,19 +3863,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.05182978588028408</v>
+        <v>0.04693978938910143</v>
       </c>
       <c r="F96" t="n">
-        <v>0.05182978588028409</v>
+        <v>0.04693978938910143</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.18%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.69%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3899,19 +3899,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.05121974055824543</v>
+        <v>0.03563919277280889</v>
       </c>
       <c r="F97" t="n">
-        <v>0.05121974055824544</v>
+        <v>0.03563919277280889</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.56%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3935,19 +3935,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.04943349195958752</v>
+        <v>0.03229557099280434</v>
       </c>
       <c r="F98" t="n">
-        <v>0.04943349195958754</v>
+        <v>0.03229557099280434</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.94%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -3971,19 +3971,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.04164635585885659</v>
+        <v>0.03060993279263494</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0416463558588566</v>
+        <v>0.03060993279263494</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.16%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.06%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -4007,19 +4007,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.03624704834575684</v>
+        <v>0.03033419722451703</v>
       </c>
       <c r="F100" t="n">
-        <v>0.03624704834575685</v>
+        <v>0.03033419722451703</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.62%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.03%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -4043,19 +4043,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.03002864339537454</v>
+        <v>0.02997237555286862</v>
       </c>
       <c r="F101" t="n">
-        <v>0.03002864339537455</v>
+        <v>0.02997237555286862</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.00%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.00%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -4135,19 +4135,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1027335695024538</v>
+        <v>0.2335976928622889</v>
       </c>
       <c r="F2" t="n">
-        <v>0.006969778495202472</v>
+        <v>0.05302921809376565</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=10.27%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.36%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4171,19 +4171,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.09652091154231966</v>
+        <v>0.2134295499021494</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006548291633037551</v>
+        <v>0.0484508301890102</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=9.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=21.34%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4207,19 +4207,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.07809443240098939</v>
+        <v>0.1053661551138105</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005298179535467795</v>
+        <v>0.02391926371689701</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.81%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=10.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4243,19 +4243,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.06968751652302239</v>
+        <v>0.08503064167267367</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00472782710070857</v>
+        <v>0.01930288089177007</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=8.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4279,19 +4279,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지자체수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05950933220535835</v>
+        <v>0.04363863425687455</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004037306071204505</v>
+        <v>0.009906444815300897</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.95%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=4.36%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4315,19 +4315,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05448633215248471</v>
+        <v>0.03056442476053147</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003696529459241427</v>
+        <v>0.006938456997056974</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=3.06%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4351,19 +4351,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04909321630624239</v>
+        <v>0.02850448037902963</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003330642991660082</v>
+        <v>0.006470827207870289</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.91%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=2.85%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4387,19 +4387,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04446676888912223</v>
+        <v>0.02491888968997853</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003016769796430951</v>
+        <v>0.005656859106067336</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=4.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=2.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4423,19 +4423,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZCT_PYHWY_AMT</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업비자부담금액</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03666790038597665</v>
+        <v>0.02480945514471095</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002487669267330406</v>
+        <v>0.005632016273516727</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.67%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=2.48%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4459,19 +4459,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>보조금전용신용카드집행건수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0365357161740591</v>
+        <v>0.02475151920898096</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002478701461752442</v>
+        <v>0.005618864185695793</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=3.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=2.48%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4551,19 +4551,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1523185775533347</v>
+        <v>0.1720786854411036</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01038651242041072</v>
+        <v>0.0481293347089442</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=15.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=17.21%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4587,19 +4587,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1017649070201782</v>
+        <v>0.09087489223856447</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006939287956237106</v>
+        <v>0.02541714038538539</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=10.18%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=9.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4623,19 +4623,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.09821405086930558</v>
+        <v>0.08293320097181266</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006697157205631743</v>
+        <v>0.02319589888674889</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=9.82%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=8.29%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4659,19 +4659,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LAF_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지자체수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.09397932612641352</v>
+        <v>0.05972465320410667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006408393866020934</v>
+        <v>0.01670461287560165</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=9.40%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=5.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4695,19 +4695,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.06452037139325294</v>
+        <v>0.05431698842707499</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004399605416554542</v>
+        <v>0.01519212277620113</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=6.45%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=5.43%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4731,19 +4731,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SBAT_BDTR_CRCD_EXE_CNT</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보조금전용신용카드집행건수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.06323154212367597</v>
+        <v>0.05205987617231388</v>
       </c>
       <c r="F7" t="n">
-        <v>0.004311720921890305</v>
+        <v>0.01456082256079916</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 보조금전용신용카드집행건수(SBAT_BDTR_CRCD_EXE_CNT). 기여도(정규화 비중)=6.32%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.21%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4767,19 +4767,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>CORP_BZR_CUMU_EXE_CNT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>법인사업자누적집행건수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04121623398826991</v>
+        <v>0.04831892160192288</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002810510268137334</v>
+        <v>0.01351450090749406</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.12%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 법인사업자누적집행건수(CORP_BZR_CUMU_EXE_CNT). 기여도(정규화 비중)=4.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4803,19 +4803,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>회계연도</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03855966753465484</v>
+        <v>0.04407116173358786</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00262936059546226</v>
+        <v>0.01232642897434177</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 회계연도(FYR). 기여도(정규화 비중)=3.86%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4839,19 +4839,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>THY_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>당해년도수행보조사업수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0350877192982458</v>
+        <v>0.04359570521695944</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002392610528203665</v>
+        <v>0.01219344675304168</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=4.36%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4875,19 +4875,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>LBST_EXE_AVG_AMT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>인건비집행평균금액</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02843315184513099</v>
+        <v>0.03278037566289588</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001938839565958195</v>
+        <v>0.009168466554240584</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=2.84%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비집행평균금액(LBST_EXE_AVG_AMT). 기여도(정규화 비중)=3.28%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -4967,19 +4967,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.06671461789117154</v>
+        <v>0.06762103693331124</v>
       </c>
       <c r="F2" t="n">
-        <v>6.671461789117155</v>
+        <v>6.762103693331121</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.76%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5003,19 +5003,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06495441989195058</v>
+        <v>0.06558865971786301</v>
       </c>
       <c r="F3" t="n">
-        <v>6.495441989195059</v>
+        <v>6.558865971786298</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.56%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5039,19 +5039,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05547755973096497</v>
+        <v>0.05638176459826573</v>
       </c>
       <c r="F4" t="n">
-        <v>5.547755973096498</v>
+        <v>5.63817645982657</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.55%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.64%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5075,19 +5075,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05417814811546744</v>
+        <v>0.04176772834277437</v>
       </c>
       <c r="F5" t="n">
-        <v>5.417814811546745</v>
+        <v>4.176772834277435</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.18%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5111,19 +5111,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05058522443296955</v>
+        <v>0.04140493817864251</v>
       </c>
       <c r="F6" t="n">
-        <v>5.058522443296956</v>
+        <v>4.140493817864249</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.14%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5147,19 +5147,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04458071949171321</v>
+        <v>0.03586576551426982</v>
       </c>
       <c r="F7" t="n">
-        <v>4.458071949171321</v>
+        <v>3.58657655142698</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.46%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=3.59%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5183,19 +5183,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04060187085898578</v>
+        <v>0.03486040528587571</v>
       </c>
       <c r="F8" t="n">
-        <v>4.060187085898579</v>
+        <v>3.486040528587569</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=3.49%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03611816776722611</v>
+        <v>0.03306797514035693</v>
       </c>
       <c r="F9" t="n">
-        <v>3.611816776722611</v>
+        <v>3.306797514035692</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.31%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5255,19 +5255,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>FLD_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>분야코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03477271178468273</v>
+        <v>0.03270175100360688</v>
       </c>
       <c r="F10" t="n">
-        <v>3.477271178468274</v>
+        <v>3.270175100360686</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 분야코드(FLD_CD). 기여도(정규화 비중)=3.27%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5291,19 +5291,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LBST_PLAN_RT</t>
+          <t>LAF_PFM_AID_BIZ_NUM</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>인건비계획비율</t>
+          <t>지자체수행보조사업수</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0344039068366</v>
+        <v>0.02953478423868656</v>
       </c>
       <c r="F11" t="n">
-        <v>3.44039068366</v>
+        <v>2.953478423868654</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -5312,7 +5312,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.44%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지자체수행보조사업수(LAF_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=2.95%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.08023667168105225</v>
+        <v>0.07427712080084094</v>
       </c>
       <c r="F2" t="n">
-        <v>8.023667168105233</v>
+        <v>7.427712080084095</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=8.02%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.43%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5419,19 +5419,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>INST_TY_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>기관유형코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.05965870228360584</v>
+        <v>0.06172011341010498</v>
       </c>
       <c r="F3" t="n">
-        <v>5.965870228360589</v>
+        <v>6.172011341010498</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.97%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.17%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05335637252486698</v>
+        <v>0.05379237014250506</v>
       </c>
       <c r="F4" t="n">
-        <v>5.335637252486702</v>
+        <v>5.379237014250506</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.34%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.38%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5491,19 +5491,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05006322781991538</v>
+        <v>0.04966963952217231</v>
       </c>
       <c r="F5" t="n">
-        <v>5.006322781991543</v>
+        <v>4.966963952217232</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.01%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.97%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5527,19 +5527,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0477082008322463</v>
+        <v>0.04847747741277377</v>
       </c>
       <c r="F6" t="n">
-        <v>4.770820083224634</v>
+        <v>4.847747741277378</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.77%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=4.85%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5563,19 +5563,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04639196940201325</v>
+        <v>0.04379704642749314</v>
       </c>
       <c r="F7" t="n">
-        <v>4.639196940201328</v>
+        <v>4.379704642749314</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.64%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.38%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5599,19 +5599,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>FLD_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>분야코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04564792997314992</v>
+        <v>0.04286335922902603</v>
       </c>
       <c r="F8" t="n">
-        <v>4.564792997314996</v>
+        <v>4.286335922902603</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.56%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 분야코드(FLD_CD). 기여도(정규화 비중)=4.29%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5644,10 +5644,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03961817449756503</v>
+        <v>0.0357887121699075</v>
       </c>
       <c r="F9" t="n">
-        <v>3.961817449756506</v>
+        <v>3.57887121699075</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.96%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.58%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5671,19 +5671,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03674398613046026</v>
+        <v>0.03530508698139623</v>
       </c>
       <c r="F10" t="n">
-        <v>3.674398613046029</v>
+        <v>3.530508698139623</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=3.53%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5707,19 +5707,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03496440685152415</v>
+        <v>0.03030561248217348</v>
       </c>
       <c r="F11" t="n">
-        <v>3.496440685152419</v>
+        <v>3.030561248217349</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=3.03%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -5799,19 +5799,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2369881283651408</v>
+        <v>0.2936518688692807</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05162945027351795</v>
+        <v>0.07443643303687553</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=29.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -5835,19 +5835,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.212956712166369</v>
+        <v>0.2751346848417932</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04639404537709613</v>
+        <v>0.06974259902791458</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=21.30%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=27.51%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -5871,19 +5871,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1194243656661127</v>
+        <v>0.07662839666667617</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02601739754282112</v>
+        <v>0.01942417236834032</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=11.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=7.66%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -5907,19 +5907,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0909143299359494</v>
+        <v>0.06540393922535705</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01980629539951562</v>
+        <v>0.01657893736975791</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=9.09%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -5943,19 +5943,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.07733439810317347</v>
+        <v>0.06234848856079634</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01684781633934174</v>
+        <v>0.01580442553141748</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.73%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=6.23%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -5979,19 +5979,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05831261422949655</v>
+        <v>0.05386240671507315</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01270379338175942</v>
+        <v>0.0136533285011588</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=5.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=5.39%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6015,19 +6015,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04704197059259392</v>
+        <v>0.02828309615157349</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01024840821450984</v>
+        <v>0.007169349205467801</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.70%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=2.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6051,19 +6051,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>CUMU_PYHWY_EXE_AMT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>누적자부담집행금액</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04169891162959222</v>
+        <v>0.02717621591082704</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009084387050488751</v>
+        <v>0.006888771331955812</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.17%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 누적자부담집행금액(CUMU_PYHWY_EXE_AMT). 기여도(정규화 비중)=2.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6087,19 +6087,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03488218925460607</v>
+        <v>0.02492786542181072</v>
       </c>
       <c r="F10" t="n">
-        <v>0.007599318446775971</v>
+        <v>0.006318847526384563</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=2.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6123,19 +6123,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03102925921657064</v>
+        <v>0.01588834345571474</v>
       </c>
       <c r="F11" t="n">
-        <v>0.006759931844677491</v>
+        <v>0.004027461559370005</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.10%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=1.59%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6215,19 +6215,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2342891032138918</v>
+        <v>0.2862142282496265</v>
       </c>
       <c r="F2" t="n">
-        <v>0.04995247063043684</v>
+        <v>0.07278511534381027</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.43%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=28.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6251,19 +6251,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.2169346663918652</v>
+        <v>0.2770658544994826</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04625235404896427</v>
+        <v>0.07045865714260663</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=21.69%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=27.71%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6287,19 +6287,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1177880874367498</v>
+        <v>0.07052062981266526</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02511344274056149</v>
+        <v>0.01793360241530789</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=11.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=7.05%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6323,19 +6323,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.08249876971091312</v>
+        <v>0.06964142052637631</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01758945386064037</v>
+        <v>0.01771001692235302</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=8.25%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.96%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6359,19 +6359,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BIZ_ENFC_ZON_DV_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>사업시행지역구분코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.07900769298714182</v>
+        <v>0.06402712331915868</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01684512599766852</v>
+        <v>0.01628228472224252</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=7.90%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=6.40%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6395,19 +6395,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.06972058767860208</v>
+        <v>0.04801746925640723</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01486503452605159</v>
+        <v>0.01221098287013628</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=6.97%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=4.80%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6431,19 +6431,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>CUMU_PYHWY_EXE_AMT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>누적자부담집행금액</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.05652179399282405</v>
+        <v>0.03201930812550288</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01205093713568295</v>
+        <v>0.008142603704212492</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=5.65%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 누적자부담집행금액(CUMU_PYHWY_EXE_AMT). 기여도(정규화 비중)=3.20%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6467,19 +6467,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.0448960878910108</v>
+        <v>0.02490518331226298</v>
       </c>
       <c r="F9" t="n">
-        <v>0.009572235673930618</v>
+        <v>0.006333460957296644</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=2.49%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6503,19 +6503,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>BIZ_ENFC_ZON_DV_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>사업시행지역구분코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03046069594404178</v>
+        <v>0.02120445925755662</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0064944847995696</v>
+        <v>0.005392356006558519</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.05%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업시행지역구분코드(BIZ_ENFC_ZON_DV_CD). 기여도(정규화 비중)=2.12%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6539,19 +6539,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02416834560818392</v>
+        <v>0.01723939777037119</v>
       </c>
       <c r="F11" t="n">
-        <v>0.005152901085104633</v>
+        <v>0.004384029273624801</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.42%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=1.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6631,19 +6631,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.2662079403069144</v>
+        <v>0.1947102492449268</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05426239799121152</v>
+        <v>0.06048206785892779</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=26.62%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=19.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6667,19 +6667,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1355325214698025</v>
+        <v>0.1458445065439734</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02762622186350999</v>
+        <v>0.04530309717054748</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=13.55%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=14.58%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6703,19 +6703,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1189286217091377</v>
+        <v>0.1120755356084346</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02424177203838218</v>
+        <v>0.03481357646185457</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=11.89%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=11.21%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6739,19 +6739,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.06474377023792785</v>
+        <v>0.1041060961037252</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01319702268854805</v>
+        <v>0.03233806126534772</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=10.41%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05747571448683674</v>
+        <v>0.07371025865394595</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01171554120706658</v>
+        <v>0.02289632355305116</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=7.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6811,19 +6811,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.04826305786287505</v>
+        <v>0.04473047863682122</v>
       </c>
       <c r="F7" t="n">
-        <v>0.009837682719038621</v>
+        <v>0.01389445011120816</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6847,19 +6847,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>CARD_FR_USE_CNT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>지자체대비보조사업금액비율</t>
+          <t>카드해외사용건수</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.03557475714486848</v>
+        <v>0.04181838710588008</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00725136759035061</v>
+        <v>0.01298987873775037</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.56%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 카드해외사용건수(CARD_FR_USE_CNT). 기여도(정규화 비중)=4.18%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6883,19 +6883,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>회계연도</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03502921300858811</v>
+        <v>0.03752316971048448</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007140166801183734</v>
+        <v>0.01165567249547711</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 회계연도(FYR). 기여도(정규화 비중)=3.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=3.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6919,19 +6919,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03132479234126444</v>
+        <v>0.02720617984399845</v>
       </c>
       <c r="F10" t="n">
-        <v>0.006385077571518238</v>
+        <v>0.008450947096457384</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.13%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=2.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -6955,19 +6955,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02879945093622435</v>
+        <v>0.02115147580470616</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00587032553134248</v>
+        <v>0.00657019853807228</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=2.88%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=2.12%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -7047,19 +7047,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.1671891555341897</v>
+        <v>0.2374525038280519</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02745224643529737</v>
+        <v>0.05506779170600101</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=16.72%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=23.75%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -7083,19 +7083,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1437700029492355</v>
+        <v>0.1477847722389224</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02360685140346158</v>
+        <v>0.03427287951810748</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=14.38%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=14.78%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -7119,19 +7119,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.1015303280210568</v>
+        <v>0.1318739484678361</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01667115056945573</v>
+        <v>0.03058298821280653</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=10.15%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=13.19%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -7155,19 +7155,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.09202722039563266</v>
+        <v>0.08831294857495794</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01511075239888809</v>
+        <v>0.02048072342328378</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=9.20%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=8.83%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -7191,19 +7191,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.0667729849588727</v>
+        <v>0.04938341619564358</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01096403909963239</v>
+        <v>0.01145254580579913</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=6.68%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=4.94%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -7236,10 +7236,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.06537482659559163</v>
+        <v>0.04835000031506613</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01073446327683619</v>
+        <v>0.01121288553884098</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.54%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=4.84%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -7263,19 +7263,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>NTS_BT_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>국세청업종코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.05499786999311703</v>
+        <v>0.03432327013113043</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009030580217020967</v>
+        <v>0.007959935817811348</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=5.50%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 국세청업종코드(NTS_BT_CD). 기여도(정규화 비중)=3.43%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -7299,19 +7299,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>BIZ_MDCN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>사업개월수</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04788692394236856</v>
+        <v>0.03111590011153352</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007862971930768625</v>
+        <v>0.007216112184386392</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=4.79%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=3.11%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -7335,19 +7335,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LAF_CPRN_AID_BIZCT_RT</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>지자체대비보조사업금액비율</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.04465368272728172</v>
+        <v>0.02727839845743778</v>
       </c>
       <c r="F10" t="n">
-        <v>0.007332077840552509</v>
+        <v>0.00632615424184052</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=4.47%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=2.73%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -7371,19 +7371,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZ_MDCN</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업개월수</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.04365967951588676</v>
+        <v>0.02534389433952774</v>
       </c>
       <c r="F11" t="n">
-        <v>0.007168863779033363</v>
+        <v>0.005877521912839634</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업개월수(BIZ_MDCN). 기여도(정규화 비중)=4.37%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=2.53%. 측정방법: 해당 변수 값을 무작위로 섞었을 때 ROC-AUC가 얼마나 떨어지는지로 측정했습니다. 하락이 클수록 그 변수가 중요합니다.</t>
         </is>
       </c>
     </row>
@@ -7463,19 +7463,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07123498568589968</v>
+        <v>0.07861920191648994</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07123498568589968</v>
+        <v>0.07861920191648994</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.86%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7499,19 +7499,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>AID_BZR_CAP_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>보조사업자시도코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06438996081869364</v>
+        <v>0.0532840740558066</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06438996081869364</v>
+        <v>0.0532840740558066</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.44%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.33%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7535,19 +7535,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AID_BZR_CAP_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>보조사업자시도코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.05839048873031386</v>
+        <v>0.053014598924571</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05839048873031386</v>
+        <v>0.053014598924571</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=5.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7571,19 +7571,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05427018714487944</v>
+        <v>0.05061020905280734</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05427018714487944</v>
+        <v>0.05061020905280734</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.43%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=5.06%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7607,19 +7607,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05358114621860463</v>
+        <v>0.04959939767759144</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05358114621860463</v>
+        <v>0.04959939767759144</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.96%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7643,19 +7643,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05098330684009479</v>
+        <v>0.03354108819730399</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05098330684009479</v>
+        <v>0.03354108819730399</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.10%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7679,19 +7679,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04893369782155989</v>
+        <v>0.03143857980808221</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04893369782155989</v>
+        <v>0.03143857980808221</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.14%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7715,19 +7715,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04303240847945023</v>
+        <v>0.03080299006641432</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04303240847945023</v>
+        <v>0.03080299006641432</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.30%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.08%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7751,19 +7751,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03644836213775499</v>
+        <v>0.02956599781773235</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03644836213775499</v>
+        <v>0.02956599781773235</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.64%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.96%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7787,19 +7787,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.02993899235451626</v>
+        <v>0.02851796918745795</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02993899235451626</v>
+        <v>0.02851796918745795</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=2.99%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=2.85%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7879,19 +7879,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07254925166059462</v>
+        <v>0.07577859416271837</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07254925166059463</v>
+        <v>0.07577859416271837</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=7.25%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.58%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7915,19 +7915,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0669679439499392</v>
+        <v>0.0534527252886216</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06696794394993921</v>
+        <v>0.0534527252886216</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.70%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=5.35%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.0584006576381239</v>
+        <v>0.05111454479859059</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05840065763812391</v>
+        <v>0.05111454479859059</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.84%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=5.11%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -7987,19 +7987,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_HSHD_DV_CD</t>
+          <t>BIZCT_PYHWY_AMT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자세대구분코드</t>
+          <t>사업비자부담금액</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.05363503924955487</v>
+        <v>0.04893739718600483</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05363503924955488</v>
+        <v>0.04893739718600483</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=5.36%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비자부담금액(BIZCT_PYHWY_AMT). 기여도(정규화 비중)=4.89%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -8023,19 +8023,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.05182978588028408</v>
+        <v>0.04693978938910143</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05182978588028409</v>
+        <v>0.04693978938910143</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=5.18%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=4.69%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -8059,19 +8059,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>MBR_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>회원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.05121974055824543</v>
+        <v>0.03563919277280889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05121974055824544</v>
+        <v>0.03563919277280889</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.12%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=3.56%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -8095,19 +8095,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MBR_NUM</t>
+          <t>BIZCT_SBAT_AMT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>회원수</t>
+          <t>사업비보조금금액</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.04943349195958752</v>
+        <v>0.03229557099280434</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04943349195958754</v>
+        <v>0.03229557099280434</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 회원수(MBR_NUM). 기여도(정규화 비중)=4.94%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.23%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -8131,19 +8131,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>LAF_CPRN_AID_BIZCT_RT</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>지자체대비보조사업금액비율</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.04164635585885659</v>
+        <v>0.03060993279263494</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0416463558588566</v>
+        <v>0.03060993279263494</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=4.16%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 지자체대비보조사업금액비율(LAF_CPRN_AID_BIZCT_RT). 기여도(정규화 비중)=3.06%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -8167,19 +8167,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>BIZCT_SUM_AMT</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>사업비합계금액</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03624704834575684</v>
+        <v>0.03033419722451703</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03624704834575685</v>
+        <v>0.03033419722451703</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.62%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.03%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
@@ -8203,19 +8203,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BIZCT_SBAT_AMT</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>사업비보조금금액</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03002864339537454</v>
+        <v>0.02997237555286862</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03002864339537455</v>
+        <v>0.02997237555286862</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비보조금금액(BIZCT_SBAT_AMT). 기여도(정규화 비중)=3.00%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=3.00%. 측정방법: 트리 분할 시 불순도(오분류)를 줄이는 데 기여한 상대 비중입니다. 값이 클수록 모델이 예측에 더 자주·강하게 사용한 변수입니다.</t>
         </is>
       </c>
     </row>
